--- a/SkiEssentials_2027_sheet.xlsx
+++ b/SkiEssentials_2027_sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REPOSITORIES\Ski selector\Ski\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{45A51CC9-657E-437D-B44E-D8B6A50D38DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD1E55E2-0F88-4A69-9B97-764E6387DBBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="1" xr2:uid="{96846C7E-69AC-4665-B520-11DF99D210AF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="1" xr2:uid="{338143C8-1D0F-486C-8A8D-CF7A9EA49C37}"/>
   </bookViews>
   <sheets>
     <sheet name="Skis" sheetId="1" r:id="rId1"/>
@@ -110,28 +110,28 @@
     <t>Form_Variable</t>
   </si>
   <si>
+    <t>Snow_Powder</t>
+  </si>
+  <si>
+    <t>Snow_Crud</t>
+  </si>
+  <si>
+    <t>Snow_FreshOnGroomed</t>
+  </si>
+  <si>
+    <t>Snow_SpringSnow</t>
+  </si>
+  <si>
     <t>Snow_Groomed</t>
   </si>
   <si>
-    <t>Snow_Hard</t>
-  </si>
-  <si>
-    <t>Snow_Icy</t>
-  </si>
-  <si>
-    <t>Snow_Slush</t>
-  </si>
-  <si>
-    <t>Snow_Variable</t>
-  </si>
-  <si>
-    <t>Snow_15cmSoft</t>
-  </si>
-  <si>
-    <t>Snow_ChoppedUp</t>
-  </si>
-  <si>
-    <t>Snow_Moguls</t>
+    <t>Snow_Hardpack</t>
+  </si>
+  <si>
+    <t>Snow_IcyPatches</t>
+  </si>
+  <si>
+    <t>Snow_Ice</t>
   </si>
   <si>
     <t>Style_Active</t>
@@ -254,7 +254,7 @@
     <t>Derived from radius 17m at 182cm, scaled to a 178cm ski (16.3m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=100mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=100mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Active = avg(quickness,edgeGrip); Cruise = avg(forgiveness,stability).</t>
@@ -302,7 +302,7 @@
     <t>Derived from radius 15.9m at 174cm, scaled to a 178cm ski (16.6m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=82mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=82mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=82mm, terrain=[Groomers, All-Mountain].</t>
@@ -332,7 +332,7 @@
     <t>Derived from radius 17.2m at 176cm, scaled to a 178cm ski (17.6m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=88mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=88mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=88mm, terrain=[Groomers, All-Mountain, Moguls].</t>
@@ -362,7 +362,7 @@
     <t>Derived from radius 17.5m at 180cm, scaled to a 178cm ski (17.1m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=92mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=92mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=92mm, terrain=[All-Mountain, Groomers, Freeride].</t>
@@ -437,7 +437,7 @@
     <t>Derived from radius 20m at 180cm, scaled to a 178cm ski (19.6m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=106mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=106mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>From site ability tags [Expert, Advanced] mapped onto the 5-level scale by distance.</t>
@@ -509,7 +509,7 @@
     <t>Derived from radius 17m at 178cm, scaled to a 178cm ski (17.0m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=94mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=94mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=94mm, terrain=[All-Mountain, Park, Groomers].</t>
@@ -566,7 +566,7 @@
     <t>Derived from radius 18m at 180cm, scaled to a 178cm ski (17.6m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=110mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=110mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=110mm, terrain=[Freeride, Powder].</t>
@@ -602,7 +602,7 @@
     <t>Derived from radius 19m at 175cm, scaled to a 178cm ski (19.7m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=90mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=90mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>From site ability tags [Intermediate, Expert] mapped onto the 5-level scale by distance.</t>
@@ -671,7 +671,7 @@
     <t>Derived from radius 18m at 178cm, scaled to a 178cm ski (18.0m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=104mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=104mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=104mm, terrain=[Freeride, All-Mountain, Powder].</t>
@@ -701,7 +701,7 @@
     <t>Derived from radius 16.5m at 179cm, scaled to a 178cm ski (16.3m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=88.5mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=88.5mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=88.5mm, terrain=[All-Mountain, Groomers, Moguls].</t>
@@ -740,7 +740,7 @@
     <t>Ideal snow: softer, variable snow. Skill level: Advanced/Expert. Use case: all-mountain/groomers/freeride skiing, rated 7.8/10 overall by 4 SkiEssentials 2027 testers.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=96mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=96mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=96mm, terrain=[All-Mountain, Groomers, Freeride].</t>
@@ -770,7 +770,7 @@
     <t>Groomers / Race</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=67mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=67mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=67mm, terrain=[Groomers, Race].</t>
@@ -806,7 +806,7 @@
     <t>Derived from radius 14.2m at 174cm, scaled to a 178cm ski (14.9m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=75mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=75mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>From site ability tags [Advanced, Advanced Intermediate] mapped onto the 5-level scale by distance.</t>
@@ -836,7 +836,7 @@
     <t>Derived from radius 14.4m at 173cm, scaled to a 178cm ski (15.2m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=84.5mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=84.5mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=84.5mm, terrain=[Groomers, All-Mountain].</t>
@@ -908,7 +908,7 @@
     <t>Derived from radius 12.5m at 165cm, scaled to a 178cm ski (14.5m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=68mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=68mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=68mm, terrain=[Groomers].</t>
@@ -932,7 +932,7 @@
     <t>Derived from radius 14.8m at 174cm, scaled to a 178cm ski (15.5m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=65mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=65mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=65mm, terrain=[Groomers, Race].</t>
@@ -962,7 +962,7 @@
     <t>Derived from radius 20m at 184cm, scaled to a 178cm ski (18.7m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=105mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=105mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=105mm, terrain=[Freeride, Powder, All-Mountain].</t>
@@ -995,7 +995,7 @@
     <t>Derived from radius 18m at 182cm, scaled to a 178cm ski (17.2m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=97mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=97mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>From site ability tags [Intermediate, Advanced Intermediate, Advanced, Expert] mapped onto the 5-level scale by distance.</t>
@@ -1085,7 +1085,7 @@
     <t>Derived from radius 13m at 178cm, scaled to a 178cm ski (13.0m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=87mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=87mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=87mm, terrain=[Groomers, Freeride, Park].</t>
@@ -1112,7 +1112,7 @@
     <t>Derived from radius 14m at 179cm, scaled to a 178cm ski (13.8m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=84mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=84mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=84mm, terrain=[Groomers, All-Mountain].</t>
@@ -1166,7 +1166,7 @@
     <t>Derived from radius 20m at 174cm, scaled to a 178cm ski (20.9m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=93mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=93mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=93mm, terrain=[All-Mountain, Groomers].</t>
@@ -1229,7 +1229,7 @@
     <t>Derived from radius 19.5m at 188cm, scaled to a 178cm ski (17.5m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=102mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=102mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=102mm, terrain=[All-Mountain, Freeride, Powder].</t>
@@ -1346,7 +1346,7 @@
     <t>Derived from radius 15m at 175cm, scaled to a 178cm ski (15.5m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=69mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=69mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=69mm, terrain=[Race, Groomers].</t>
@@ -1460,7 +1460,7 @@
     <t>Derived from radius 14m at 170cm, scaled to a 178cm ski (15.3m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=80mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=80mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>From site ability tags [Intermediate, Advanced Intermediate] mapped onto the 5-level scale by distance.</t>
@@ -1508,7 +1508,7 @@
     <t>Derived from radius 15.5m at 174cm, scaled to a 178cm ski (16.2m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=76mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=76mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=76mm, terrain=[Groomers, All-Mountain].</t>
@@ -1598,7 +1598,7 @@
     <t>Derived from radius 18m at 176cm, scaled to a 178cm ski (18.4m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=103mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=103mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=103mm, terrain=[All-Mountain, Freeride, Park].</t>
@@ -1622,7 +1622,7 @@
     <t>Derived from radius 13.5m at 174cm, scaled to a 178cm ski (14.1m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=79mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=79mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=79mm, terrain=[Groomers, All-Mountain].</t>
@@ -1649,7 +1649,7 @@
     <t>Derived from radius 16m at 178cm, scaled to a 178cm ski (16.0m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=89mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=89mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=89mm, terrain=[Groomers, All-Mountain, Moguls].</t>
@@ -1820,7 +1820,7 @@
     <t>Derived from radius 14m at 172cm, scaled to a 178cm ski (15.0m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=74mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=74mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=74mm, terrain=[Groomers, Race, All-Mountain].</t>
@@ -1847,7 +1847,7 @@
     <t>Derived from radius 18.1m at 180cm, scaled to a 178cm ski (17.7m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=101mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=101mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=101mm, terrain=[Freeride, Park, All-Mountain].</t>
@@ -1868,7 +1868,7 @@
     <t>Ideal snow: a mix of groomed and softer conditions. Skill level: Advanced Intermediate/Expert. Use case: freeride/park/all-mountain skiing, rated 7.4/10 overall by 8 SkiEssentials 2027 testers.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=91mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=91mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=91mm, terrain=[Freeride, Park, All-Mountain].</t>
@@ -2039,7 +2039,7 @@
     <t>Derived from radius 15m at 174cm, scaled to a 178cm ski (15.7m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=83mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=83mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=83mm, terrain=[Groomers, All-Mountain, Moguls].</t>
@@ -2078,7 +2078,7 @@
     <t>Derived from radius 16m at 174cm, scaled to a 178cm ski (16.7m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=86mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=86mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=86mm, terrain=[All-Mountain, Groomers, Moguls].</t>
@@ -2219,7 +2219,7 @@
     <t>Derived from radius 19m at 183cm, scaled to a 178cm ski (18.0m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=99mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=99mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=99mm, terrain=[All-Mountain, Freeride, Groomers].</t>
@@ -2438,7 +2438,7 @@
     <t>Derived from radius 13m at 165cm, scaled to a 178cm ski (15.1m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=66mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=66mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=66mm, terrain=[Groomers, Race].</t>
@@ -2483,7 +2483,7 @@
     <t>Derived from radius 17.5m at 178cm, scaled to a 178cm ski (17.5m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=72mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=72mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=72mm, terrain=[Race, Groomers].</t>
@@ -2528,7 +2528,7 @@
     <t>Ideal snow: firm groomers and hardpack. Skill level: Intermediate/Advanced. Use case: groomers/all-mountain skiing, rated 7.3/10 overall by 15 SkiEssentials 2027 testers.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=85mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=85mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=85mm, terrain=[Groomers, All-Mountain].</t>
@@ -2813,7 +2813,7 @@
     <t>Ideal snow: a mix of groomed and softer conditions. Skill level: Expert/Advanced. Use case: groomers/all-mountain skiing, rated 7.6/10 overall by 8 SkiEssentials 2027 testers.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=78mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=78mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=78mm, terrain=[Groomers, All-Mountain].</t>
@@ -2939,7 +2939,7 @@
     <t>Derived from radius 21m at 187cm, scaled to a 178cm ski (19.0m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=111mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=111mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=111mm, terrain=[Freeride, Powder, Big Mountain].</t>
@@ -3059,7 +3059,7 @@
     <t>Ideal snow: a mix of groomed and softer conditions. Skill level: Advanced/Expert. Use case: park/all-mountain skiing, rated 7.6/10 overall by 5 SkiEssentials 2027 testers.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=95mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=95mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=95mm, terrain=[Park, All-Mountain].</t>
@@ -3239,7 +3239,7 @@
     <t>Derived from radius 19.2m at 184cm, scaled to a 178cm ski (18.0m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=107mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=107mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=107mm, terrain=[All-Mountain, Big Mountain, Freeride].</t>
@@ -3368,7 +3368,7 @@
     <t>Derived from radius 16.8m at 181cm, scaled to a 178cm ski (16.2m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=98mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=98mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=98mm, terrain=[Freeride, All-Mountain, Powder].</t>
@@ -3530,7 +3530,7 @@
     <t>Derived from radius 17.4m at 184cm, scaled to a 178cm ski (16.3m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=108mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=108mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=108mm, terrain=[All-Mountain, Freeride, Powder].</t>
@@ -3731,7 +3731,7 @@
     <t>Ideal snow: firm groomers and hardpack. Skill level: Advanced/Expert. Use case: race/groomers skiing, rated 8.2/10 overall by 6 SkiEssentials 2027 testers.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=70mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=70mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=70mm, terrain=[Race, Groomers].</t>
@@ -4055,7 +4055,7 @@
     <t>Derived from radius 14m at 173cm, scaled to a 178cm ski (14.8m), via the app’s own turnRadiusFit() curve.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=77mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=77mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=77mm, terrain=[Groomers, All-Mountain].</t>
@@ -4079,7 +4079,7 @@
     <t>Ideal snow: firm groomers and hardpack. Skill level: Advanced/Expert. Use case: groomers/race skiing, rated 8.3/10 overall by 4 SkiEssentials 2027 testers.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=71mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=71mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=71mm, terrain=[Groomers, Race].</t>
@@ -4103,7 +4103,7 @@
     <t>Ideal snow: firm groomers and hardpack. Skill level: Advanced Intermediate/Expert. Use case: groomers/all-mountain skiing, rated 8.1/10 overall by 7 SkiEssentials 2027 testers.</t>
   </si>
   <si>
-    <t>hard/icy from edgeGrip; groomed avg(edgeGrip,stability); slush/soft15 from floatation+forgiveness+width bonus (mid=73mm); chopped from stability+floatation; moguls avg(quickness,forgiveness).</t>
+    <t>Powder from floatation+playfulness+width bonus (mid=73mm); Crud from stability+floatation; Fresh snow on groomed from floatation+forgiveness+width bonus; Spring snow from floatation+forgiveness+width bonus; Groomed avg(edgeGrip,stability); Hardpack edgeGrip; Hardpack with icy patches edgeGrip*0.6+stability*0.25+forgiveness*0.15-0.3; Ice edgeGrip-0.5.</t>
   </si>
   <si>
     <t>Rule: race if Race-tagged &amp; mid&lt;=70; narrowfs if mid&lt;=75; frontside if site-categorized frontside; else all-mountain. mid=73mm, terrain=[Groomers, All-Mountain].</t>
@@ -5864,7 +5864,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A150A7E0-BFDF-425B-B6BF-C5ABF8040955}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1405FEFF-43CD-4C63-90A3-280FFE07FF15}">
   <dimension ref="A1:BJ208"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -6145,28 +6145,28 @@
         <v>8.1</v>
       </c>
       <c r="AD2">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AE2">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="AF2">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AG2">
         <v>7.8</v>
       </c>
       <c r="AH2">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
       <c r="AI2">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
       <c r="AJ2">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AK2">
-        <v>7.7</v>
+        <v>6.4</v>
       </c>
       <c r="AL2">
         <v>7.5</v>
@@ -6327,28 +6327,28 @@
         <v>5.8</v>
       </c>
       <c r="AD3">
-        <v>7.7</v>
+        <v>4</v>
       </c>
       <c r="AE3">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="AF3">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="AG3">
         <v>5.2</v>
       </c>
       <c r="AH3">
-        <v>5.8</v>
+        <v>7.7</v>
       </c>
       <c r="AI3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AJ3">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="AK3">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
       <c r="AL3">
         <v>7.4</v>
@@ -6509,28 +6509,28 @@
         <v>7</v>
       </c>
       <c r="AD4">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="AE4">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="AF4">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="AG4">
         <v>7</v>
       </c>
       <c r="AH4">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AI4">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="AJ4">
         <v>6.4</v>
       </c>
       <c r="AK4">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="AL4">
         <v>7</v>
@@ -6691,13 +6691,13 @@
         <v>7.7</v>
       </c>
       <c r="AD5">
-        <v>7.7</v>
+        <v>6.5</v>
       </c>
       <c r="AE5">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AF5">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="AG5">
         <v>6.9</v>
@@ -6706,13 +6706,13 @@
         <v>7.7</v>
       </c>
       <c r="AI5">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AJ5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AK5">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="AL5">
         <v>7.7</v>
@@ -6873,28 +6873,28 @@
         <v>7.2</v>
       </c>
       <c r="AD6">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AE6">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="AF6">
-        <v>6.3</v>
+        <v>7.2</v>
       </c>
       <c r="AG6">
         <v>7.3</v>
       </c>
       <c r="AH6">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AI6">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AJ6">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="AK6">
-        <v>7.4</v>
+        <v>6.3</v>
       </c>
       <c r="AL6">
         <v>7.2</v>
@@ -7055,28 +7055,28 @@
         <v>8</v>
       </c>
       <c r="AD7">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AE7">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AF7">
-        <v>6.5</v>
+        <v>8.1</v>
       </c>
       <c r="AG7">
         <v>8</v>
       </c>
       <c r="AH7">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AI7">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="AJ7">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AK7">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="AL7">
         <v>7</v>
@@ -7237,28 +7237,28 @@
         <v>6.7</v>
       </c>
       <c r="AD8">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="AE8">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
       <c r="AF8">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="AG8">
         <v>6.6</v>
       </c>
       <c r="AH8">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="AI8">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="AJ8">
+        <v>6</v>
+      </c>
+      <c r="AK8">
         <v>5.8</v>
-      </c>
-      <c r="AK8">
-        <v>6.7</v>
       </c>
       <c r="AL8">
         <v>6.3</v>
@@ -7419,28 +7419,28 @@
         <v>7.3</v>
       </c>
       <c r="AD9">
-        <v>7.4</v>
+        <v>6.3</v>
       </c>
       <c r="AE9">
-        <v>6</v>
+        <v>7.9</v>
       </c>
       <c r="AF9">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AG9">
         <v>6.5</v>
       </c>
       <c r="AH9">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="AI9">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AJ9">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="AK9">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="AL9">
         <v>6.9</v>
@@ -7601,28 +7601,28 @@
         <v>7.2</v>
       </c>
       <c r="AD10">
-        <v>6.4</v>
+        <v>7.9</v>
       </c>
       <c r="AE10">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="AF10">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="AG10">
         <v>7.8</v>
       </c>
       <c r="AH10">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AI10">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="AJ10">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="AK10">
-        <v>7.1</v>
+        <v>5.9</v>
       </c>
       <c r="AL10">
         <v>6.7</v>
@@ -7783,28 +7783,28 @@
         <v>8</v>
       </c>
       <c r="AD11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE11">
-        <v>6.8</v>
+        <v>7.7</v>
       </c>
       <c r="AF11">
-        <v>6.3</v>
+        <v>9.1</v>
       </c>
       <c r="AG11">
         <v>9</v>
       </c>
       <c r="AH11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI11">
-        <v>9.1</v>
+        <v>6.8</v>
       </c>
       <c r="AJ11">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="AK11">
-        <v>8.1</v>
+        <v>6.3</v>
       </c>
       <c r="AL11">
         <v>7.6</v>
@@ -7965,28 +7965,28 @@
         <v>7.7</v>
       </c>
       <c r="AD12">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="AE12">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AF12">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="AG12">
         <v>6.6</v>
       </c>
       <c r="AH12">
-        <v>7.7</v>
+        <v>6.3</v>
       </c>
       <c r="AI12">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="AJ12">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AK12">
-        <v>7.5</v>
+        <v>6.1</v>
       </c>
       <c r="AL12">
         <v>7.3</v>
@@ -8147,28 +8147,28 @@
         <v>7.4</v>
       </c>
       <c r="AD13">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="AE13">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="AF13">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AG13">
         <v>7.7</v>
       </c>
       <c r="AH13">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="AI13">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="AJ13">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="AK13">
-        <v>8.6</v>
+        <v>6</v>
       </c>
       <c r="AL13">
         <v>7.7</v>
@@ -8329,28 +8329,28 @@
         <v>7.7</v>
       </c>
       <c r="AD14">
-        <v>7.5</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AE14">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="AF14">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AG14">
         <v>7.6</v>
       </c>
       <c r="AH14">
+        <v>7.5</v>
+      </c>
+      <c r="AI14">
         <v>7.7</v>
       </c>
-      <c r="AI14">
-        <v>7.8</v>
-      </c>
       <c r="AJ14">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="AK14">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AL14">
         <v>7.7</v>
@@ -8511,28 +8511,28 @@
         <v>7.2</v>
       </c>
       <c r="AD15">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AE15">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="AF15">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="AG15">
         <v>6.9</v>
       </c>
       <c r="AH15">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AI15">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="AJ15">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="AK15">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="AL15">
         <v>7.4</v>
@@ -8693,28 +8693,28 @@
         <v>7.3</v>
       </c>
       <c r="AD16">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="AE16">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="AF16">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="AG16">
         <v>7.1</v>
       </c>
       <c r="AH16">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="AI16">
+        <v>7.5</v>
+      </c>
+      <c r="AJ16">
         <v>7.1</v>
       </c>
-      <c r="AJ16">
-        <v>7.3</v>
-      </c>
       <c r="AK16">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AL16">
         <v>7.6</v>
@@ -8875,28 +8875,28 @@
         <v>7.2</v>
       </c>
       <c r="AD17">
-        <v>7.3</v>
+        <v>8.1</v>
       </c>
       <c r="AE17">
+        <v>7.2</v>
+      </c>
+      <c r="AF17">
         <v>7.8</v>
-      </c>
-      <c r="AF17">
-        <v>7.3</v>
       </c>
       <c r="AG17">
         <v>7.6</v>
       </c>
       <c r="AH17">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="AI17">
         <v>7.8</v>
       </c>
       <c r="AJ17">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="AK17">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="AL17">
         <v>7.2</v>
@@ -9057,28 +9057,28 @@
         <v>5.2</v>
       </c>
       <c r="AD18">
-        <v>8.6</v>
+        <v>3.5</v>
       </c>
       <c r="AE18">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="AF18">
-        <v>8.5</v>
+        <v>4.3</v>
       </c>
       <c r="AG18">
         <v>4.5</v>
       </c>
       <c r="AH18">
-        <v>5.2</v>
+        <v>8.6</v>
       </c>
       <c r="AI18">
-        <v>4.3</v>
+        <v>9</v>
       </c>
       <c r="AJ18">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AK18">
-        <v>6.4</v>
+        <v>8.5</v>
       </c>
       <c r="AL18">
         <v>8.1</v>
@@ -9239,28 +9239,28 @@
         <v>6.5</v>
       </c>
       <c r="AD19">
-        <v>7.5</v>
+        <v>4.3</v>
       </c>
       <c r="AE19">
-        <v>7.7</v>
+        <v>6.5</v>
       </c>
       <c r="AF19">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="AG19">
         <v>5.7</v>
       </c>
       <c r="AH19">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AI19">
-        <v>5.5</v>
+        <v>7.7</v>
       </c>
       <c r="AJ19">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="AK19">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AL19">
         <v>7.2</v>
@@ -9421,28 +9421,28 @@
         <v>6.5</v>
       </c>
       <c r="AD20">
-        <v>8.9</v>
+        <v>5.4</v>
       </c>
       <c r="AE20">
-        <v>8.8000000000000007</v>
+        <v>8.1</v>
       </c>
       <c r="AF20">
-        <v>8.3000000000000007</v>
+        <v>6.1</v>
       </c>
       <c r="AG20">
         <v>6.1</v>
       </c>
       <c r="AH20">
-        <v>6.5</v>
+        <v>8.9</v>
       </c>
       <c r="AI20">
-        <v>6.1</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="AJ20">
-        <v>8.1</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AK20">
-        <v>7.3</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AL20">
         <v>8.6</v>
@@ -9603,28 +9603,28 @@
         <v>5.3</v>
       </c>
       <c r="AD21">
-        <v>8.6999999999999993</v>
+        <v>2.4</v>
       </c>
       <c r="AE21">
-        <v>8.8000000000000007</v>
+        <v>6.7</v>
       </c>
       <c r="AF21">
-        <v>8.3000000000000007</v>
+        <v>3.5</v>
       </c>
       <c r="AG21">
         <v>3.8</v>
       </c>
       <c r="AH21">
-        <v>5.3</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AI21">
-        <v>3.5</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="AJ21">
-        <v>6.7</v>
+        <v>8</v>
       </c>
       <c r="AK21">
-        <v>6.9</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AL21">
         <v>8.4</v>
@@ -9785,28 +9785,28 @@
         <v>6.8</v>
       </c>
       <c r="AD22">
-        <v>8.5</v>
+        <v>5.6</v>
       </c>
       <c r="AE22">
-        <v>8.3000000000000007</v>
+        <v>8</v>
       </c>
       <c r="AF22">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AG22">
         <v>6.7</v>
       </c>
       <c r="AH22">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="AI22">
-        <v>6.6</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AJ22">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="AK22">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="AL22">
         <v>8.1</v>
@@ -9967,28 +9967,28 @@
         <v>7.5</v>
       </c>
       <c r="AD23">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="AE23">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AF23">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="AG23">
         <v>7.4</v>
       </c>
       <c r="AH23">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AI23">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="AJ23">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AK23">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="AL23">
         <v>8</v>
@@ -10146,28 +10146,28 @@
         <v>5.4</v>
       </c>
       <c r="AD24">
-        <v>8.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="AE24">
-        <v>8.6999999999999993</v>
+        <v>6.3</v>
       </c>
       <c r="AF24">
-        <v>8.1999999999999993</v>
+        <v>3.2</v>
       </c>
       <c r="AG24">
         <v>3.5</v>
       </c>
       <c r="AH24">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="AI24">
-        <v>3.2</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AJ24">
-        <v>6.3</v>
+        <v>7.7</v>
       </c>
       <c r="AK24">
-        <v>6.3</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AL24">
         <v>8</v>
@@ -10328,28 +10328,28 @@
         <v>7.2</v>
       </c>
       <c r="AD25">
-        <v>7.3</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AE25">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AF25">
-        <v>6.5</v>
+        <v>7.9</v>
       </c>
       <c r="AG25">
         <v>7.8</v>
       </c>
       <c r="AH25">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="AI25">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="AJ25">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AK25">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="AL25">
         <v>7</v>
@@ -10510,28 +10510,28 @@
         <v>6.9</v>
       </c>
       <c r="AD26">
+        <v>6.9</v>
+      </c>
+      <c r="AE26">
         <v>7.2</v>
       </c>
-      <c r="AE26">
-        <v>7</v>
-      </c>
       <c r="AF26">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="AG26">
         <v>7</v>
       </c>
       <c r="AH26">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="AI26">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="AJ26">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AK26">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AL26">
         <v>7</v>
@@ -10692,13 +10692,13 @@
         <v>7</v>
       </c>
       <c r="AD27">
-        <v>7</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="AE27">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AF27">
-        <v>6.5</v>
+        <v>8.9</v>
       </c>
       <c r="AG27">
         <v>8.8000000000000007</v>
@@ -10707,13 +10707,13 @@
         <v>7</v>
       </c>
       <c r="AI27">
-        <v>8.9</v>
+        <v>7</v>
       </c>
       <c r="AJ27">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
       <c r="AK27">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="AL27">
         <v>8</v>
@@ -10871,28 +10871,28 @@
         <v>7.2</v>
       </c>
       <c r="AD28">
-        <v>7.3</v>
+        <v>6.3</v>
       </c>
       <c r="AE28">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="AF28">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="AG28">
         <v>6.5</v>
       </c>
       <c r="AH28">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="AI28">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AJ28">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="AK28">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="AL28">
         <v>7.4</v>
@@ -11053,28 +11053,28 @@
         <v>7.9</v>
       </c>
       <c r="AD29">
-        <v>7.1</v>
+        <v>6.3</v>
       </c>
       <c r="AE29">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AF29">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="AG29">
         <v>6.8</v>
       </c>
       <c r="AH29">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="AI29">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AJ29">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AK29">
-        <v>8.4</v>
+        <v>6.7</v>
       </c>
       <c r="AL29">
         <v>8</v>
@@ -11232,28 +11232,28 @@
         <v>6.9</v>
       </c>
       <c r="AD30">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="AE30">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="AF30">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AG30">
         <v>6.5</v>
       </c>
       <c r="AH30">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="AI30">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
       <c r="AJ30">
         <v>7.1</v>
       </c>
       <c r="AK30">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="AL30">
         <v>8.1999999999999993</v>
@@ -11414,28 +11414,28 @@
         <v>7.4</v>
       </c>
       <c r="AD31">
-        <v>7.2</v>
+        <v>6.1</v>
       </c>
       <c r="AE31">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
       <c r="AF31">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="AG31">
         <v>6.4</v>
       </c>
       <c r="AH31">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AI31">
-        <v>6.3</v>
+        <v>7.3</v>
       </c>
       <c r="AJ31">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="AK31">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="AL31">
         <v>7.7</v>
@@ -11596,28 +11596,28 @@
         <v>8</v>
       </c>
       <c r="AD32">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AE32">
+        <v>7.7</v>
+      </c>
+      <c r="AF32">
         <v>7.6</v>
-      </c>
-      <c r="AF32">
-        <v>7.1</v>
       </c>
       <c r="AG32">
         <v>7.6</v>
       </c>
       <c r="AH32">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AI32">
         <v>7.6</v>
       </c>
       <c r="AJ32">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="AK32">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="AL32">
         <v>8</v>
@@ -11778,28 +11778,28 @@
         <v>7.8</v>
       </c>
       <c r="AD33">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="AE33">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="AF33">
-        <v>6.7</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AG33">
         <v>8.1999999999999993</v>
       </c>
       <c r="AH33">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="AI33">
-        <v>8.1999999999999993</v>
+        <v>7.2</v>
       </c>
       <c r="AJ33">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AK33">
-        <v>7.8</v>
+        <v>6.7</v>
       </c>
       <c r="AL33">
         <v>7.7</v>
@@ -11960,28 +11960,28 @@
         <v>6.9</v>
       </c>
       <c r="AD34">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AE34">
         <v>8.6999999999999993</v>
       </c>
       <c r="AF34">
-        <v>8.1999999999999993</v>
+        <v>7.5</v>
       </c>
       <c r="AG34">
         <v>7.4</v>
       </c>
       <c r="AH34">
-        <v>6.9</v>
+        <v>9</v>
       </c>
       <c r="AI34">
-        <v>7.5</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AJ34">
-        <v>8.6999999999999993</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AK34">
-        <v>6.5</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AL34">
         <v>7.7</v>
@@ -12142,28 +12142,28 @@
         <v>6.1</v>
       </c>
       <c r="AD35">
-        <v>8.5</v>
+        <v>4.3</v>
       </c>
       <c r="AE35">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="AF35">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="AG35">
         <v>5.7</v>
       </c>
       <c r="AH35">
-        <v>6.1</v>
+        <v>8.5</v>
       </c>
       <c r="AI35">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="AJ35">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="AK35">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AL35">
         <v>8</v>
@@ -12324,28 +12324,28 @@
         <v>7.2</v>
       </c>
       <c r="AD36">
-        <v>8.4</v>
+        <v>6.7</v>
       </c>
       <c r="AE36">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
       <c r="AF36">
-        <v>8.1</v>
+        <v>6.9</v>
       </c>
       <c r="AG36">
         <v>6.9</v>
       </c>
       <c r="AH36">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AI36">
-        <v>6.9</v>
+        <v>8.6</v>
       </c>
       <c r="AJ36">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="AK36">
-        <v>7.2</v>
+        <v>8.1</v>
       </c>
       <c r="AL36">
         <v>8.1</v>
@@ -12506,28 +12506,28 @@
         <v>7</v>
       </c>
       <c r="AD37">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
       <c r="AE37">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="AF37">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AG37">
         <v>7.2</v>
       </c>
       <c r="AH37">
+        <v>7.8</v>
+      </c>
+      <c r="AI37">
+        <v>7.5</v>
+      </c>
+      <c r="AJ37">
+        <v>7.3</v>
+      </c>
+      <c r="AK37">
         <v>7</v>
-      </c>
-      <c r="AI37">
-        <v>7.2</v>
-      </c>
-      <c r="AJ37">
-        <v>7.7</v>
-      </c>
-      <c r="AK37">
-        <v>7.4</v>
       </c>
       <c r="AL37">
         <v>7.7</v>
@@ -12688,28 +12688,28 @@
         <v>8.5</v>
       </c>
       <c r="AD38">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="AE38">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="AF38">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG38">
         <v>8.4</v>
       </c>
       <c r="AH38">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="AI38">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
       <c r="AJ38">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="AK38">
-        <v>8.1999999999999993</v>
+        <v>6.6</v>
       </c>
       <c r="AL38">
         <v>7.6</v>
@@ -12870,28 +12870,28 @@
         <v>5.7</v>
       </c>
       <c r="AD39">
-        <v>9.1999999999999993</v>
+        <v>3.3</v>
       </c>
       <c r="AE39">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="AF39">
-        <v>8.9</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="AG39">
         <v>4.3</v>
       </c>
       <c r="AH39">
-        <v>5.7</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="AI39">
-        <v>4.0999999999999996</v>
+        <v>9.4</v>
       </c>
       <c r="AJ39">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AK39">
-        <v>6.7</v>
+        <v>8.9</v>
       </c>
       <c r="AL39">
         <v>8.6999999999999993</v>
@@ -13052,28 +13052,28 @@
         <v>6.7</v>
       </c>
       <c r="AD40">
-        <v>9.1999999999999993</v>
+        <v>4</v>
       </c>
       <c r="AE40">
-        <v>9.6999999999999993</v>
+        <v>7.4</v>
       </c>
       <c r="AF40">
-        <v>9.1999999999999993</v>
+        <v>5.3</v>
       </c>
       <c r="AG40">
         <v>5.7</v>
       </c>
       <c r="AH40">
-        <v>6.7</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="AI40">
-        <v>5.3</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="AJ40">
-        <v>7.4</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="AK40">
-        <v>7.9</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="AL40">
         <v>8.9</v>
@@ -13234,13 +13234,13 @@
         <v>7.6</v>
       </c>
       <c r="AD41">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AE41">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="AF41">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="AG41">
         <v>8.4</v>
@@ -13249,13 +13249,13 @@
         <v>7.6</v>
       </c>
       <c r="AI41">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="AJ41">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AK41">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="AL41">
         <v>7.6</v>
@@ -13416,28 +13416,28 @@
         <v>7.4</v>
       </c>
       <c r="AD42">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AE42">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="AF42">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AG42">
         <v>7.5</v>
       </c>
       <c r="AH42">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AI42">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
       <c r="AJ42">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="AK42">
-        <v>7.1</v>
+        <v>6.4</v>
       </c>
       <c r="AL42">
         <v>7</v>
@@ -13598,28 +13598,28 @@
         <v>7</v>
       </c>
       <c r="AD43">
-        <v>7.5</v>
+        <v>5.6</v>
       </c>
       <c r="AE43">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="AF43">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
       <c r="AG43">
         <v>6.9</v>
       </c>
       <c r="AH43">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AI43">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="AJ43">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="AK43">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AL43">
         <v>7.4</v>
@@ -13780,28 +13780,28 @@
         <v>5.7</v>
       </c>
       <c r="AD44">
-        <v>7.8</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AE44">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AF44">
-        <v>7.3</v>
+        <v>5.8</v>
       </c>
       <c r="AG44">
         <v>5.9</v>
       </c>
       <c r="AH44">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="AI44">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="AJ44">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="AK44">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="AL44">
         <v>7.3</v>
@@ -13962,28 +13962,28 @@
         <v>5.2</v>
       </c>
       <c r="AD45">
-        <v>8.4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="AE45">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="AF45">
-        <v>8</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="AG45">
         <v>5.2</v>
       </c>
       <c r="AH45">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="AI45">
-        <v>5.0999999999999996</v>
+        <v>8.5</v>
       </c>
       <c r="AJ45">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="AK45">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AL45">
         <v>7.9</v>
@@ -14144,28 +14144,28 @@
         <v>5.9</v>
       </c>
       <c r="AD46">
-        <v>8.6999999999999993</v>
+        <v>3.4</v>
       </c>
       <c r="AE46">
-        <v>8.6999999999999993</v>
+        <v>7.3</v>
       </c>
       <c r="AF46">
-        <v>8.1999999999999993</v>
+        <v>4.5</v>
       </c>
       <c r="AG46">
         <v>4.7</v>
       </c>
       <c r="AH46">
-        <v>5.9</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AI46">
-        <v>4.5</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AJ46">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="AK46">
-        <v>6.5</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AL46">
         <v>7.8</v>
@@ -14326,28 +14326,28 @@
         <v>6.7</v>
       </c>
       <c r="AD47">
-        <v>6.6</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AE47">
-        <v>6.1</v>
+        <v>7.3</v>
       </c>
       <c r="AF47">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="AG47">
         <v>7.9</v>
       </c>
       <c r="AH47">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="AI47">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="AJ47">
-        <v>7.3</v>
+        <v>6.2</v>
       </c>
       <c r="AK47">
-        <v>6.9</v>
+        <v>5.6</v>
       </c>
       <c r="AL47">
         <v>6.5</v>
@@ -14508,28 +14508,28 @@
         <v>7</v>
       </c>
       <c r="AD48">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="AE48">
         <v>6.8</v>
       </c>
-      <c r="AE48">
-        <v>7</v>
-      </c>
       <c r="AF48">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="AG48">
         <v>7.5</v>
       </c>
       <c r="AH48">
+        <v>6.8</v>
+      </c>
+      <c r="AI48">
         <v>7</v>
       </c>
-      <c r="AI48">
-        <v>7.6</v>
-      </c>
       <c r="AJ48">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="AK48">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="AL48">
         <v>7</v>
@@ -14690,28 +14690,28 @@
         <v>6.8</v>
       </c>
       <c r="AD49">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="AE49">
-        <v>6.1</v>
+        <v>6.9</v>
       </c>
       <c r="AF49">
-        <v>5.6</v>
+        <v>7.5</v>
       </c>
       <c r="AG49">
         <v>7.5</v>
       </c>
       <c r="AH49">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="AI49">
-        <v>7.5</v>
+        <v>6.1</v>
       </c>
       <c r="AJ49">
-        <v>6.9</v>
+        <v>6.1</v>
       </c>
       <c r="AK49">
-        <v>7.1</v>
+        <v>5.6</v>
       </c>
       <c r="AL49">
         <v>6.6</v>
@@ -14872,28 +14872,28 @@
         <v>7.4</v>
       </c>
       <c r="AD50">
-        <v>7.7</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AE50">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AF50">
-        <v>7.3</v>
+        <v>5.8</v>
       </c>
       <c r="AG50">
         <v>6</v>
       </c>
       <c r="AH50">
+        <v>7.7</v>
+      </c>
+      <c r="AI50">
+        <v>7.8</v>
+      </c>
+      <c r="AJ50">
         <v>7.4</v>
       </c>
-      <c r="AI50">
-        <v>5.8</v>
-      </c>
-      <c r="AJ50">
-        <v>6.8</v>
-      </c>
       <c r="AK50">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="AL50">
         <v>8</v>
@@ -15054,28 +15054,28 @@
         <v>7.6</v>
       </c>
       <c r="AD51">
+        <v>7</v>
+      </c>
+      <c r="AE51">
         <v>7.3</v>
       </c>
-      <c r="AE51">
-        <v>6.9</v>
-      </c>
       <c r="AF51">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AG51">
         <v>7.3</v>
       </c>
       <c r="AH51">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="AI51">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="AJ51">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="AK51">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="AL51">
         <v>7.6</v>
@@ -15236,28 +15236,28 @@
         <v>7.6</v>
       </c>
       <c r="AD52">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="AE52">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="AF52">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AG52">
         <v>7</v>
       </c>
       <c r="AH52">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="AI52">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="AJ52">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="AK52">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="AL52">
         <v>7.8</v>
@@ -15418,28 +15418,28 @@
         <v>6.9</v>
       </c>
       <c r="AD53">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="AE53">
-        <v>7.3</v>
+        <v>6.2</v>
       </c>
       <c r="AF53">
-        <v>6.8</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="AG53">
         <v>5.4</v>
       </c>
       <c r="AH53">
+        <v>7.2</v>
+      </c>
+      <c r="AI53">
+        <v>7.3</v>
+      </c>
+      <c r="AJ53">
         <v>6.9</v>
       </c>
-      <c r="AI53">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="AJ53">
-        <v>6.2</v>
-      </c>
       <c r="AK53">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AL53">
         <v>7.5</v>
@@ -15600,28 +15600,28 @@
         <v>7.4</v>
       </c>
       <c r="AD54">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AE54">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AF54">
-        <v>6.3</v>
+        <v>7.3</v>
       </c>
       <c r="AG54">
         <v>7.3</v>
       </c>
       <c r="AH54">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AI54">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="AJ54">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AK54">
-        <v>7.3</v>
+        <v>6.3</v>
       </c>
       <c r="AL54">
         <v>7.2</v>
@@ -15782,28 +15782,28 @@
         <v>7.2</v>
       </c>
       <c r="AD55">
-        <v>6.9</v>
+        <v>8</v>
       </c>
       <c r="AE55">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="AF55">
-        <v>6.3</v>
+        <v>7.7</v>
       </c>
       <c r="AG55">
         <v>7.7</v>
       </c>
       <c r="AH55">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="AI55">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="AJ55">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="AK55">
-        <v>7.1</v>
+        <v>6.3</v>
       </c>
       <c r="AL55">
         <v>7.1</v>
@@ -15964,28 +15964,28 @@
         <v>7.9</v>
       </c>
       <c r="AD56">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="AE56">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="AF56">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="AG56">
         <v>7.8</v>
       </c>
       <c r="AH56">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="AI56">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="AJ56">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="AK56">
-        <v>8.1999999999999993</v>
+        <v>6.5</v>
       </c>
       <c r="AL56">
         <v>7.8</v>
@@ -16146,28 +16146,28 @@
         <v>6.5</v>
       </c>
       <c r="AD57">
-        <v>8.1999999999999993</v>
+        <v>7.2</v>
       </c>
       <c r="AE57">
-        <v>8.1999999999999993</v>
+        <v>7.8</v>
       </c>
       <c r="AF57">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="AG57">
         <v>7.1</v>
       </c>
       <c r="AH57">
-        <v>6.5</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AI57">
-        <v>7.1</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AJ57">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AK57">
-        <v>6.2</v>
+        <v>7.7</v>
       </c>
       <c r="AL57">
         <v>7.2</v>
@@ -16328,28 +16328,28 @@
         <v>6.8</v>
       </c>
       <c r="AD58">
-        <v>7.7</v>
+        <v>6.5</v>
       </c>
       <c r="AE58">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="AF58">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AG58">
         <v>6.8</v>
       </c>
       <c r="AH58">
-        <v>6.8</v>
+        <v>7.7</v>
       </c>
       <c r="AI58">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="AJ58">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AK58">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="AL58">
         <v>7.3</v>
@@ -16510,28 +16510,28 @@
         <v>6.2</v>
       </c>
       <c r="AD59">
-        <v>8.3000000000000007</v>
+        <v>4.2</v>
       </c>
       <c r="AE59">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AF59">
-        <v>8.1</v>
+        <v>5</v>
       </c>
       <c r="AG59">
         <v>5.2</v>
       </c>
       <c r="AH59">
-        <v>6.2</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AI59">
-        <v>5</v>
+        <v>8.6</v>
       </c>
       <c r="AJ59">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AK59">
-        <v>7.2</v>
+        <v>8.1</v>
       </c>
       <c r="AL59">
         <v>8.3000000000000007</v>
@@ -16692,28 +16692,28 @@
         <v>8.6999999999999993</v>
       </c>
       <c r="AD60">
+        <v>8.5</v>
+      </c>
+      <c r="AE60">
         <v>6.5</v>
       </c>
-      <c r="AE60">
-        <v>6.9</v>
-      </c>
       <c r="AF60">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AG60">
         <v>8.5</v>
       </c>
       <c r="AH60">
-        <v>8.6999999999999993</v>
+        <v>6.5</v>
       </c>
       <c r="AI60">
-        <v>8.4</v>
+        <v>6.9</v>
       </c>
       <c r="AJ60">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="AK60">
-        <v>9.1</v>
+        <v>6.4</v>
       </c>
       <c r="AL60">
         <v>8.1</v>
@@ -16874,28 +16874,28 @@
         <v>7.5</v>
       </c>
       <c r="AD61">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="AE61">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="AF61">
-        <v>5.4</v>
+        <v>6.9</v>
       </c>
       <c r="AG61">
         <v>7</v>
       </c>
       <c r="AH61">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="AI61">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="AJ61">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="AK61">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="AL61">
         <v>6.9</v>
@@ -17056,28 +17056,28 @@
         <v>7.9</v>
       </c>
       <c r="AD62">
-        <v>6.9</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AE62">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AF62">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="AG62">
         <v>8</v>
       </c>
       <c r="AH62">
-        <v>7.9</v>
+        <v>6.9</v>
       </c>
       <c r="AI62">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AJ62">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
       <c r="AK62">
-        <v>7.8</v>
+        <v>6.3</v>
       </c>
       <c r="AL62">
         <v>7.4</v>
@@ -17238,28 +17238,28 @@
         <v>7.9</v>
       </c>
       <c r="AD63">
-        <v>7.5</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="AE63">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="AF63">
-        <v>6.8</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AG63">
         <v>8.6999999999999993</v>
       </c>
       <c r="AH63">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="AI63">
-        <v>8.6999999999999993</v>
+        <v>7.3</v>
       </c>
       <c r="AJ63">
-        <v>7.9</v>
+        <v>7.2</v>
       </c>
       <c r="AK63">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="AL63">
         <v>8</v>
@@ -17420,28 +17420,28 @@
         <v>6</v>
       </c>
       <c r="AD64">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AE64">
-        <v>5.3</v>
+        <v>6.1</v>
       </c>
       <c r="AF64">
-        <v>4.8</v>
+        <v>6.3</v>
       </c>
       <c r="AG64">
         <v>6.3</v>
       </c>
       <c r="AH64">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AI64">
-        <v>6.3</v>
+        <v>5.3</v>
       </c>
       <c r="AJ64">
-        <v>6.1</v>
+        <v>5.3</v>
       </c>
       <c r="AK64">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="AL64">
         <v>6</v>
@@ -17602,28 +17602,28 @@
         <v>6.8</v>
       </c>
       <c r="AD65">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AE65">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AF65">
-        <v>5.0999999999999996</v>
+        <v>6.5</v>
       </c>
       <c r="AG65">
         <v>6.7</v>
       </c>
       <c r="AH65">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AI65">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="AJ65">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AK65">
-        <v>8</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="AL65">
         <v>6.8</v>
@@ -17784,28 +17784,28 @@
         <v>8</v>
       </c>
       <c r="AD66">
-        <v>7.9</v>
+        <v>6.7</v>
       </c>
       <c r="AE66">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="AF66">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="AG66">
         <v>7.2</v>
       </c>
       <c r="AH66">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="AI66">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="AJ66">
         <v>7.5</v>
       </c>
       <c r="AK66">
-        <v>8.3000000000000007</v>
+        <v>7.3</v>
       </c>
       <c r="AL66">
         <v>8.1999999999999993</v>
@@ -17966,13 +17966,13 @@
         <v>6.6</v>
       </c>
       <c r="AD67">
+        <v>6.7</v>
+      </c>
+      <c r="AE67">
+        <v>6.8</v>
+      </c>
+      <c r="AF67">
         <v>6.6</v>
-      </c>
-      <c r="AE67">
-        <v>6.2</v>
-      </c>
-      <c r="AF67">
-        <v>5.7</v>
       </c>
       <c r="AG67">
         <v>6.6</v>
@@ -17981,13 +17981,13 @@
         <v>6.6</v>
       </c>
       <c r="AI67">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AJ67">
-        <v>6.8</v>
+        <v>6.1</v>
       </c>
       <c r="AK67">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="AL67">
         <v>6.7</v>
@@ -18151,10 +18151,10 @@
         <v>7.3</v>
       </c>
       <c r="AE68">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="AF68">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="AG68">
         <v>7.1</v>
@@ -18163,13 +18163,13 @@
         <v>7.3</v>
       </c>
       <c r="AI68">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="AJ68">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="AK68">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="AL68">
         <v>7.6</v>
@@ -18330,28 +18330,28 @@
         <v>5.8</v>
       </c>
       <c r="AD69">
-        <v>6.3</v>
+        <v>4.5</v>
       </c>
       <c r="AE69">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="AF69">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="AG69">
         <v>6.4</v>
       </c>
       <c r="AH69">
+        <v>6.3</v>
+      </c>
+      <c r="AI69">
+        <v>6.3</v>
+      </c>
+      <c r="AJ69">
+        <v>6.3</v>
+      </c>
+      <c r="AK69">
         <v>5.8</v>
-      </c>
-      <c r="AI69">
-        <v>6.1</v>
-      </c>
-      <c r="AJ69">
-        <v>6</v>
-      </c>
-      <c r="AK69">
-        <v>8</v>
       </c>
       <c r="AL69">
         <v>7.2</v>
@@ -18509,28 +18509,28 @@
         <v>6.6</v>
       </c>
       <c r="AD70">
-        <v>7.3</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AE70">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
       <c r="AF70">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="AG70">
         <v>6</v>
       </c>
       <c r="AH70">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="AI70">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="AJ70">
+        <v>6.9</v>
+      </c>
+      <c r="AK70">
         <v>6.7</v>
-      </c>
-      <c r="AK70">
-        <v>7.1</v>
       </c>
       <c r="AL70">
         <v>7.3</v>
@@ -18691,28 +18691,28 @@
         <v>5.7</v>
       </c>
       <c r="AD71">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="AE71">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="AF71">
-        <v>6.9</v>
+        <v>5.8</v>
       </c>
       <c r="AG71">
         <v>5.9</v>
       </c>
       <c r="AH71">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="AI71">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="AJ71">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="AK71">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="AL71">
         <v>7.2</v>
@@ -18873,25 +18873,25 @@
         <v>7</v>
       </c>
       <c r="AD72">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
       <c r="AE72">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="AF72">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AG72">
         <v>6.8</v>
       </c>
       <c r="AH72">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="AI72">
-        <v>6.6</v>
+        <v>7.9</v>
       </c>
       <c r="AJ72">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AK72">
         <v>7.4</v>
@@ -19055,28 +19055,28 @@
         <v>6.8</v>
       </c>
       <c r="AD73">
-        <v>6.4</v>
+        <v>7.9</v>
       </c>
       <c r="AE73">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AF73">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="AG73">
         <v>7</v>
       </c>
       <c r="AH73">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AI73">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="AJ73">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="AK73">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AL73">
         <v>6.5</v>
@@ -19237,28 +19237,28 @@
         <v>7.5</v>
       </c>
       <c r="AD74">
-        <v>7.9</v>
+        <v>5.2</v>
       </c>
       <c r="AE74">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="AF74">
-        <v>7.3</v>
+        <v>6.3</v>
       </c>
       <c r="AG74">
         <v>6.5</v>
       </c>
       <c r="AH74">
+        <v>7.9</v>
+      </c>
+      <c r="AI74">
+        <v>7.8</v>
+      </c>
+      <c r="AJ74">
         <v>7.5</v>
       </c>
-      <c r="AI74">
-        <v>6.3</v>
-      </c>
-      <c r="AJ74">
+      <c r="AK74">
         <v>7.3</v>
-      </c>
-      <c r="AK74">
-        <v>7.7</v>
       </c>
       <c r="AL74">
         <v>7.8</v>
@@ -19419,28 +19419,28 @@
         <v>7.4</v>
       </c>
       <c r="AD75">
-        <v>7.7</v>
+        <v>4.8</v>
       </c>
       <c r="AE75">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="AF75">
-        <v>6.9</v>
+        <v>5.7</v>
       </c>
       <c r="AG75">
         <v>5.9</v>
       </c>
       <c r="AH75">
+        <v>7.7</v>
+      </c>
+      <c r="AI75">
         <v>7.4</v>
       </c>
-      <c r="AI75">
-        <v>5.7</v>
-      </c>
       <c r="AJ75">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="AK75">
-        <v>7.7</v>
+        <v>6.9</v>
       </c>
       <c r="AL75">
         <v>7.8</v>
@@ -19601,28 +19601,28 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="AD76">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="AE76">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="AF76">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="AG76">
         <v>7</v>
       </c>
       <c r="AH76">
-        <v>8.3000000000000007</v>
+        <v>7.2</v>
       </c>
       <c r="AI76">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AJ76">
         <v>6.9</v>
       </c>
       <c r="AK76">
-        <v>8.1999999999999993</v>
+        <v>6.5</v>
       </c>
       <c r="AL76">
         <v>7.7</v>
@@ -19783,28 +19783,28 @@
         <v>7</v>
       </c>
       <c r="AD77">
-        <v>7.3</v>
+        <v>6.3</v>
       </c>
       <c r="AE77">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="AF77">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AG77">
         <v>6.6</v>
       </c>
       <c r="AH77">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="AI77">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="AJ77">
         <v>6.9</v>
       </c>
       <c r="AK77">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="AL77">
         <v>7.4</v>
@@ -19965,28 +19965,28 @@
         <v>7.8</v>
       </c>
       <c r="AD78">
+        <v>7.7</v>
+      </c>
+      <c r="AE78">
         <v>7</v>
       </c>
-      <c r="AE78">
-        <v>7.1</v>
-      </c>
       <c r="AF78">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AG78">
         <v>7.6</v>
       </c>
       <c r="AH78">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AI78">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="AJ78">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AK78">
-        <v>7.7</v>
+        <v>6.6</v>
       </c>
       <c r="AL78">
         <v>7.5</v>
@@ -20147,28 +20147,28 @@
         <v>7.9</v>
       </c>
       <c r="AD79">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="AE79">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="AF79">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="AG79">
         <v>7.2</v>
       </c>
       <c r="AH79">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="AI79">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AJ79">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="AK79">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="AL79">
         <v>7.7</v>
@@ -20329,28 +20329,28 @@
         <v>7.7</v>
       </c>
       <c r="AD80">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="AE80">
+        <v>7.7</v>
+      </c>
+      <c r="AF80">
         <v>7.6</v>
-      </c>
-      <c r="AF80">
-        <v>7.1</v>
       </c>
       <c r="AG80">
         <v>7.6</v>
       </c>
       <c r="AH80">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="AI80">
         <v>7.6</v>
       </c>
       <c r="AJ80">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="AK80">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="AL80">
         <v>7.6</v>
@@ -20511,25 +20511,25 @@
         <v>6</v>
       </c>
       <c r="AD81">
-        <v>5.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AE81">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="AF81">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="AG81">
         <v>4.7</v>
       </c>
       <c r="AH81">
+        <v>5.8</v>
+      </c>
+      <c r="AI81">
         <v>6</v>
       </c>
-      <c r="AI81">
-        <v>4.7</v>
-      </c>
       <c r="AJ81">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AK81">
         <v>5.5</v>
@@ -20693,28 +20693,28 @@
         <v>8.1</v>
       </c>
       <c r="AD82">
-        <v>7.2</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AE82">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AF82">
-        <v>6.5</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AG82">
         <v>8.1999999999999993</v>
       </c>
       <c r="AH82">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
       <c r="AI82">
-        <v>8.1999999999999993</v>
+        <v>7</v>
       </c>
       <c r="AJ82">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="AK82">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="AL82">
         <v>7.5</v>
@@ -20875,28 +20875,28 @@
         <v>7.6</v>
       </c>
       <c r="AD83">
-        <v>7.5</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AE83">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="AF83">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AG83">
         <v>8</v>
       </c>
       <c r="AH83">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="AI83">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="AJ83">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="AK83">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="AL83">
         <v>7.6</v>
@@ -21057,28 +21057,28 @@
         <v>6.9</v>
       </c>
       <c r="AD84">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="AE84">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="AF84">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AG84">
         <v>6.5</v>
       </c>
       <c r="AH84">
-        <v>6.9</v>
+        <v>6.2</v>
       </c>
       <c r="AI84">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AJ84">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
       <c r="AK84">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="AL84">
         <v>6.4</v>
@@ -21239,28 +21239,28 @@
         <v>7.5</v>
       </c>
       <c r="AD85">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="AE85">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="AF85">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="AG85">
         <v>6.9</v>
       </c>
       <c r="AH85">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="AI85">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="AJ85">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AK85">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AL85">
         <v>7.4</v>
@@ -21421,28 +21421,28 @@
         <v>7.3</v>
       </c>
       <c r="AD86">
+        <v>7.3</v>
+      </c>
+      <c r="AE86">
         <v>7.1</v>
       </c>
-      <c r="AE86">
-        <v>7</v>
-      </c>
       <c r="AF86">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="AG86">
         <v>7.2</v>
       </c>
       <c r="AH86">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="AI86">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AJ86">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="AK86">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="AL86">
         <v>7.1</v>
@@ -21600,28 +21600,28 @@
         <v>7.5</v>
       </c>
       <c r="AD87">
-        <v>8.8000000000000007</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="AE87">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="AF87">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="AG87">
         <v>6.3</v>
       </c>
       <c r="AH87">
-        <v>7.5</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="AI87">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AJ87">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="AK87">
-        <v>8.3000000000000007</v>
+        <v>8.5</v>
       </c>
       <c r="AL87">
         <v>8.9</v>
@@ -21779,28 +21779,28 @@
         <v>3.8</v>
       </c>
       <c r="AD88">
-        <v>7.8</v>
+        <v>1.8</v>
       </c>
       <c r="AE88">
-        <v>8.3000000000000007</v>
+        <v>5.7</v>
       </c>
       <c r="AF88">
-        <v>7.8</v>
+        <v>2.8</v>
       </c>
       <c r="AG88">
         <v>3</v>
       </c>
       <c r="AH88">
-        <v>3.8</v>
+        <v>7.8</v>
       </c>
       <c r="AI88">
-        <v>2.8</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AJ88">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="AK88">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="AL88">
         <v>7.4</v>
@@ -21958,28 +21958,28 @@
         <v>3.5</v>
       </c>
       <c r="AD89">
-        <v>8.5</v>
+        <v>1</v>
       </c>
       <c r="AE89">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="AF89">
-        <v>7.5</v>
+        <v>1.9</v>
       </c>
       <c r="AG89">
         <v>2.2000000000000002</v>
       </c>
       <c r="AH89">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="AI89">
-        <v>1.9</v>
+        <v>8</v>
       </c>
       <c r="AJ89">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AK89">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="AL89">
         <v>7.5</v>
@@ -22137,28 +22137,28 @@
         <v>5.7</v>
       </c>
       <c r="AD90">
-        <v>8.3000000000000007</v>
+        <v>3.4</v>
       </c>
       <c r="AE90">
-        <v>8.5</v>
+        <v>6.7</v>
       </c>
       <c r="AF90">
-        <v>8</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="AG90">
         <v>4.5999999999999996</v>
       </c>
       <c r="AH90">
-        <v>5.7</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AI90">
-        <v>4.4000000000000004</v>
+        <v>8.5</v>
       </c>
       <c r="AJ90">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="AK90">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AL90">
         <v>7.9</v>
@@ -22319,28 +22319,28 @@
         <v>6</v>
       </c>
       <c r="AD91">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="AE91">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
       <c r="AF91">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="AG91">
         <v>5.9</v>
       </c>
       <c r="AH91">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI91">
-        <v>5.9</v>
+        <v>8.1</v>
       </c>
       <c r="AJ91">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="AK91">
-        <v>6.3</v>
+        <v>7.6</v>
       </c>
       <c r="AL91">
         <v>7.3</v>
@@ -22501,28 +22501,28 @@
         <v>5.3</v>
       </c>
       <c r="AD92">
-        <v>7.6</v>
+        <v>3.3</v>
       </c>
       <c r="AE92">
-        <v>7.7</v>
+        <v>6.4</v>
       </c>
       <c r="AF92">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="AG92">
         <v>4.4000000000000004</v>
       </c>
       <c r="AH92">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="AI92">
-        <v>4.2</v>
+        <v>7.7</v>
       </c>
       <c r="AJ92">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AK92">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="AL92">
         <v>7.1</v>
@@ -22683,28 +22683,28 @@
         <v>6.2</v>
       </c>
       <c r="AD93">
-        <v>6.4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="AE93">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="AF93">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="AG93">
         <v>5.4</v>
       </c>
       <c r="AH93">
+        <v>6.4</v>
+      </c>
+      <c r="AI93">
+        <v>6.5</v>
+      </c>
+      <c r="AJ93">
         <v>6.2</v>
       </c>
-      <c r="AI93">
-        <v>5.2</v>
-      </c>
-      <c r="AJ93">
-        <v>5.7</v>
-      </c>
       <c r="AK93">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="AL93">
         <v>7</v>
@@ -22865,28 +22865,28 @@
         <v>5.3</v>
       </c>
       <c r="AD94">
-        <v>6.1</v>
+        <v>3.8</v>
       </c>
       <c r="AE94">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="AF94">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="AG94">
         <v>5.5</v>
       </c>
       <c r="AH94">
-        <v>5.3</v>
+        <v>6.1</v>
       </c>
       <c r="AI94">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AJ94">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AK94">
-        <v>7.1</v>
+        <v>5.7</v>
       </c>
       <c r="AL94">
         <v>6.7</v>
@@ -23047,28 +23047,28 @@
         <v>6.7</v>
       </c>
       <c r="AD95">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="AE95">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
       <c r="AF95">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AG95">
         <v>6.7</v>
       </c>
       <c r="AH95">
-        <v>6.7</v>
+        <v>5.9</v>
       </c>
       <c r="AI95">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="AJ95">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="AK95">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="AL95">
         <v>6.6</v>
@@ -23232,25 +23232,25 @@
         <v>7.5</v>
       </c>
       <c r="AE96">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AF96">
-        <v>6.3</v>
+        <v>7.7</v>
       </c>
       <c r="AG96">
         <v>7.7</v>
       </c>
       <c r="AH96">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="AI96">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="AJ96">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AK96">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="AL96">
         <v>6.6</v>
@@ -23411,28 +23411,28 @@
         <v>7.1</v>
       </c>
       <c r="AD97">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="AE97">
         <v>8.1999999999999993</v>
       </c>
-      <c r="AE97">
-        <v>8</v>
-      </c>
       <c r="AF97">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="AG97">
         <v>8.3000000000000007</v>
       </c>
       <c r="AH97">
-        <v>7.1</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AI97">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AJ97">
-        <v>8.1999999999999993</v>
+        <v>7.7</v>
       </c>
       <c r="AK97">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="AL97">
         <v>7.4</v>
@@ -23593,28 +23593,28 @@
         <v>6.7</v>
       </c>
       <c r="AD98">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="AE98">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AF98">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="AG98">
         <v>6.6</v>
       </c>
       <c r="AH98">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="AI98">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AJ98">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="AK98">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="AL98">
         <v>7.2</v>
@@ -23775,10 +23775,10 @@
         <v>7.7</v>
       </c>
       <c r="AD99">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="AE99">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="AF99">
         <v>7.4</v>
@@ -23787,16 +23787,16 @@
         <v>7.5</v>
       </c>
       <c r="AH99">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="AI99">
+        <v>7.9</v>
+      </c>
+      <c r="AJ99">
+        <v>7.6</v>
+      </c>
+      <c r="AK99">
         <v>7.4</v>
-      </c>
-      <c r="AJ99">
-        <v>7.7</v>
-      </c>
-      <c r="AK99">
-        <v>7.7</v>
       </c>
       <c r="AL99">
         <v>7.7</v>
@@ -23957,28 +23957,28 @@
         <v>7.6</v>
       </c>
       <c r="AD100">
-        <v>7.3</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AE100">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="AF100">
-        <v>7</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AG100">
         <v>8.1999999999999993</v>
       </c>
       <c r="AH100">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="AI100">
-        <v>8.1999999999999993</v>
+        <v>7.5</v>
       </c>
       <c r="AJ100">
         <v>7.2</v>
       </c>
       <c r="AK100">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="AL100">
         <v>7.7</v>
@@ -24139,28 +24139,28 @@
         <v>7</v>
       </c>
       <c r="AD101">
-        <v>6.5</v>
+        <v>3.9</v>
       </c>
       <c r="AE101">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="AF101">
-        <v>6.5</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="AG101">
         <v>5.4</v>
       </c>
       <c r="AH101">
+        <v>6.5</v>
+      </c>
+      <c r="AI101">
         <v>7</v>
       </c>
-      <c r="AI101">
-        <v>5.0999999999999996</v>
-      </c>
       <c r="AJ101">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="AK101">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AL101">
         <v>7.3</v>
@@ -24321,28 +24321,28 @@
         <v>7.6</v>
       </c>
       <c r="AD102">
+        <v>6.6</v>
+      </c>
+      <c r="AE102">
         <v>5.9</v>
       </c>
-      <c r="AE102">
-        <v>6</v>
-      </c>
       <c r="AF102">
-        <v>5.5</v>
+        <v>6.9</v>
       </c>
       <c r="AG102">
         <v>7</v>
       </c>
       <c r="AH102">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="AI102">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="AJ102">
         <v>5.9</v>
       </c>
       <c r="AK102">
-        <v>7.9</v>
+        <v>5.5</v>
       </c>
       <c r="AL102">
         <v>7.2</v>
@@ -24503,28 +24503,28 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="AD103">
-        <v>8</v>
+        <v>2.6</v>
       </c>
       <c r="AE103">
-        <v>8.1999999999999993</v>
+        <v>6.4</v>
       </c>
       <c r="AF103">
-        <v>7.7</v>
+        <v>3.6</v>
       </c>
       <c r="AG103">
         <v>3.8</v>
       </c>
       <c r="AH103">
-        <v>4.9000000000000004</v>
+        <v>8</v>
       </c>
       <c r="AI103">
-        <v>3.6</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AJ103">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="AK103">
-        <v>6.1</v>
+        <v>7.7</v>
       </c>
       <c r="AL103">
         <v>7.7</v>
@@ -24685,28 +24685,28 @@
         <v>6.4</v>
       </c>
       <c r="AD104">
-        <v>7.7</v>
+        <v>4.7</v>
       </c>
       <c r="AE104">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="AF104">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="AG104">
         <v>5.7</v>
       </c>
       <c r="AH104">
-        <v>6.4</v>
+        <v>7.7</v>
       </c>
       <c r="AI104">
-        <v>5.6</v>
+        <v>7.5</v>
       </c>
       <c r="AJ104">
         <v>7.1</v>
       </c>
       <c r="AK104">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="AL104">
         <v>7.5</v>
@@ -24867,28 +24867,28 @@
         <v>5.8</v>
       </c>
       <c r="AD105">
-        <v>8.3000000000000007</v>
+        <v>4.2</v>
       </c>
       <c r="AE105">
-        <v>8.3000000000000007</v>
+        <v>7.2</v>
       </c>
       <c r="AF105">
-        <v>7.8</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="AG105">
         <v>5.2</v>
       </c>
       <c r="AH105">
-        <v>5.8</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AI105">
-        <v>5.0999999999999996</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AJ105">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AK105">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AL105">
         <v>8</v>
@@ -25049,28 +25049,28 @@
         <v>5.8</v>
       </c>
       <c r="AD106">
-        <v>9.3000000000000007</v>
+        <v>3</v>
       </c>
       <c r="AE106">
-        <v>9.3000000000000007</v>
+        <v>7.4</v>
       </c>
       <c r="AF106">
-        <v>8.8000000000000007</v>
+        <v>3.8</v>
       </c>
       <c r="AG106">
         <v>4</v>
       </c>
       <c r="AH106">
-        <v>5.8</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="AI106">
-        <v>3.8</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="AJ106">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AK106">
-        <v>6.8</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="AL106">
         <v>8.8000000000000007</v>
@@ -25231,28 +25231,28 @@
         <v>6.5</v>
       </c>
       <c r="AD107">
-        <v>8.6999999999999993</v>
+        <v>3.9</v>
       </c>
       <c r="AE107">
-        <v>8.6999999999999993</v>
+        <v>7.3</v>
       </c>
       <c r="AF107">
-        <v>8.1999999999999993</v>
+        <v>4.8</v>
       </c>
       <c r="AG107">
         <v>5.0999999999999996</v>
       </c>
       <c r="AH107">
-        <v>6.5</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AI107">
-        <v>4.8</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AJ107">
-        <v>7.3</v>
+        <v>8.1</v>
       </c>
       <c r="AK107">
-        <v>7.7</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AL107">
         <v>8.6999999999999993</v>
@@ -25413,28 +25413,28 @@
         <v>6.4</v>
       </c>
       <c r="AD108">
-        <v>6.7</v>
+        <v>5.2</v>
       </c>
       <c r="AE108">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="AF108">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="AG108">
         <v>6.2</v>
       </c>
       <c r="AH108">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="AI108">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="AJ108">
         <v>6.4</v>
       </c>
       <c r="AK108">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="AL108">
         <v>6.7</v>
@@ -25595,28 +25595,28 @@
         <v>7.9</v>
       </c>
       <c r="AD109">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="AE109">
         <v>7.8</v>
       </c>
-      <c r="AE109">
-        <v>7.7</v>
-      </c>
       <c r="AF109">
-        <v>7.2</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AG109">
         <v>8.1999999999999993</v>
       </c>
       <c r="AH109">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="AI109">
-        <v>8.1999999999999993</v>
+        <v>7.7</v>
       </c>
       <c r="AJ109">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="AK109">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AL109">
         <v>7.6</v>
@@ -25777,28 +25777,28 @@
         <v>7</v>
       </c>
       <c r="AD110">
-        <v>8</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="AE110">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="AF110">
-        <v>7</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="AG110">
         <v>9.1</v>
       </c>
       <c r="AH110">
+        <v>8</v>
+      </c>
+      <c r="AI110">
+        <v>7.5</v>
+      </c>
+      <c r="AJ110">
+        <v>7.5</v>
+      </c>
+      <c r="AK110">
         <v>7</v>
-      </c>
-      <c r="AI110">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="AJ110">
-        <v>8.6</v>
-      </c>
-      <c r="AK110">
-        <v>7.8</v>
       </c>
       <c r="AL110">
         <v>7.5</v>
@@ -25959,28 +25959,28 @@
         <v>7.5</v>
       </c>
       <c r="AD111">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="AE111">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="AF111">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="AG111">
         <v>5.9</v>
       </c>
       <c r="AH111">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="AI111">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="AJ111">
-        <v>5.9</v>
+        <v>6.7</v>
       </c>
       <c r="AK111">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="AL111">
         <v>7.8</v>
@@ -26141,28 +26141,28 @@
         <v>7</v>
       </c>
       <c r="AD112">
-        <v>7.4</v>
+        <v>6.1</v>
       </c>
       <c r="AE112">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AF112">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="AG112">
         <v>6.5</v>
       </c>
       <c r="AH112">
+        <v>7.4</v>
+      </c>
+      <c r="AI112">
         <v>7</v>
       </c>
-      <c r="AI112">
-        <v>6.4</v>
-      </c>
       <c r="AJ112">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="AK112">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="AL112">
         <v>7.3</v>
@@ -26323,28 +26323,28 @@
         <v>7.1</v>
       </c>
       <c r="AD113">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AE113">
-        <v>5.3</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="AF113">
-        <v>4.8</v>
+        <v>6.3</v>
       </c>
       <c r="AG113">
         <v>6.6</v>
       </c>
       <c r="AH113">
-        <v>7.1</v>
+        <v>5.2</v>
       </c>
       <c r="AI113">
-        <v>6.3</v>
+        <v>5.3</v>
       </c>
       <c r="AJ113">
-        <v>5.0999999999999996</v>
+        <v>5.3</v>
       </c>
       <c r="AK113">
-        <v>7.9</v>
+        <v>4.8</v>
       </c>
       <c r="AL113">
         <v>6.6</v>
@@ -26505,28 +26505,28 @@
         <v>7.8</v>
       </c>
       <c r="AD114">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="AE114">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AF114">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="AG114">
         <v>7</v>
       </c>
       <c r="AH114">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="AI114">
+        <v>7.2</v>
+      </c>
+      <c r="AJ114">
         <v>7</v>
       </c>
-      <c r="AJ114">
-        <v>7.4</v>
-      </c>
       <c r="AK114">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="AL114">
         <v>7.4</v>
@@ -26687,28 +26687,28 @@
         <v>8</v>
       </c>
       <c r="AD115">
-        <v>6.7</v>
+        <v>5.9</v>
       </c>
       <c r="AE115">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="AF115">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="AG115">
         <v>6.3</v>
       </c>
       <c r="AH115">
-        <v>8</v>
+        <v>6.7</v>
       </c>
       <c r="AI115">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="AJ115">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="AK115">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="AL115">
         <v>7.7</v>
@@ -26869,28 +26869,28 @@
         <v>7.1</v>
       </c>
       <c r="AD116">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="AE116">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AF116">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AG116">
         <v>6.7</v>
       </c>
       <c r="AH116">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="AI116">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AJ116">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="AK116">
-        <v>7.3</v>
+        <v>5.9</v>
       </c>
       <c r="AL116">
         <v>7</v>
@@ -27051,28 +27051,28 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="AD117">
-        <v>6.4</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AE117">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="AF117">
-        <v>6</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AG117">
         <v>8.3000000000000007</v>
       </c>
       <c r="AH117">
-        <v>8.3000000000000007</v>
+        <v>6.4</v>
       </c>
       <c r="AI117">
-        <v>8.1999999999999993</v>
+        <v>6.5</v>
       </c>
       <c r="AJ117">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AK117">
-        <v>8.1</v>
+        <v>6</v>
       </c>
       <c r="AL117">
         <v>7.2</v>
@@ -27233,28 +27233,28 @@
         <v>6</v>
       </c>
       <c r="AD118">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="AE118">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AF118">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="AG118">
         <v>5</v>
       </c>
       <c r="AH118">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AI118">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="AJ118">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AK118">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="AL118">
         <v>5.5</v>
@@ -27409,28 +27409,28 @@
         <v>6.9</v>
       </c>
       <c r="AD119">
-        <v>9.3000000000000007</v>
+        <v>4.7</v>
       </c>
       <c r="AE119">
-        <v>9.1</v>
+        <v>8.1</v>
       </c>
       <c r="AF119">
-        <v>8.6</v>
+        <v>5.3</v>
       </c>
       <c r="AG119">
         <v>5.3</v>
       </c>
       <c r="AH119">
-        <v>6.9</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="AI119">
-        <v>5.3</v>
+        <v>9.1</v>
       </c>
       <c r="AJ119">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="AK119">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AL119">
         <v>8.9</v>
@@ -27591,28 +27591,28 @@
         <v>6.5</v>
       </c>
       <c r="AD120">
-        <v>8.8000000000000007</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="AE120">
-        <v>8.8000000000000007</v>
+        <v>7.4</v>
       </c>
       <c r="AF120">
-        <v>8.3000000000000007</v>
+        <v>5</v>
       </c>
       <c r="AG120">
         <v>5.2</v>
       </c>
       <c r="AH120">
-        <v>6.5</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="AI120">
-        <v>5</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="AJ120">
-        <v>7.4</v>
+        <v>8.1</v>
       </c>
       <c r="AK120">
-        <v>7.4</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AL120">
         <v>8.6</v>
@@ -27773,28 +27773,28 @@
         <v>6.9</v>
       </c>
       <c r="AD121">
-        <v>8.6999999999999993</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="AE121">
-        <v>8.8000000000000007</v>
+        <v>7.7</v>
       </c>
       <c r="AF121">
-        <v>8.3000000000000007</v>
+        <v>5.8</v>
       </c>
       <c r="AG121">
         <v>5.9</v>
       </c>
       <c r="AH121">
-        <v>6.9</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AI121">
-        <v>5.8</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="AJ121">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="AK121">
-        <v>7.3</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AL121">
         <v>8.5</v>
@@ -27955,28 +27955,28 @@
         <v>7.1</v>
       </c>
       <c r="AD122">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="AE122">
-        <v>9</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AF122">
-        <v>8.5</v>
+        <v>6.6</v>
       </c>
       <c r="AG122">
         <v>6.7</v>
       </c>
       <c r="AH122">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="AI122">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="AJ122">
-        <v>8.1999999999999993</v>
+        <v>8.4</v>
       </c>
       <c r="AK122">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AL122">
         <v>8.5</v>
@@ -28137,10 +28137,10 @@
         <v>7.4</v>
       </c>
       <c r="AD123">
-        <v>8.1999999999999993</v>
+        <v>7.8</v>
       </c>
       <c r="AE123">
-        <v>8.1999999999999993</v>
+        <v>7.9</v>
       </c>
       <c r="AF123">
         <v>7.7</v>
@@ -28149,16 +28149,16 @@
         <v>7.7</v>
       </c>
       <c r="AH123">
-        <v>7.4</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AI123">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="AJ123">
         <v>7.7</v>
       </c>
-      <c r="AJ123">
-        <v>7.9</v>
-      </c>
       <c r="AK123">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="AL123">
         <v>7.8</v>
@@ -28319,28 +28319,28 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="AD124">
-        <v>8.1</v>
+        <v>9.6</v>
       </c>
       <c r="AE124">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="AF124">
-        <v>7.3</v>
+        <v>9</v>
       </c>
       <c r="AG124">
         <v>8.9</v>
       </c>
       <c r="AH124">
-        <v>8.1999999999999993</v>
+        <v>8.1</v>
       </c>
       <c r="AI124">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AJ124">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="AK124">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
       <c r="AL124">
         <v>7.9</v>
@@ -28501,28 +28501,28 @@
         <v>7.1</v>
       </c>
       <c r="AD125">
-        <v>7.9</v>
+        <v>6.3</v>
       </c>
       <c r="AE125">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="AF125">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AG125">
         <v>6.6</v>
       </c>
       <c r="AH125">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="AI125">
-        <v>6.6</v>
+        <v>7.9</v>
       </c>
       <c r="AJ125">
         <v>7.4</v>
       </c>
       <c r="AK125">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AL125">
         <v>7.5</v>
@@ -28683,28 +28683,28 @@
         <v>6</v>
       </c>
       <c r="AD126">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AE126">
-        <v>8.3000000000000007</v>
+        <v>6.8</v>
       </c>
       <c r="AF126">
-        <v>7.8</v>
+        <v>5.2</v>
       </c>
       <c r="AG126">
         <v>5.3</v>
       </c>
       <c r="AH126">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI126">
-        <v>5.2</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AJ126">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AK126">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AL126">
         <v>8.1999999999999993</v>
@@ -28865,28 +28865,28 @@
         <v>6.5</v>
       </c>
       <c r="AD127">
-        <v>7.7</v>
+        <v>5.9</v>
       </c>
       <c r="AE127">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AF127">
-        <v>7.1</v>
+        <v>6.2</v>
       </c>
       <c r="AG127">
         <v>6.2</v>
       </c>
       <c r="AH127">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="AI127">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AJ127">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="AK127">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="AL127">
         <v>7.4</v>
@@ -29047,28 +29047,28 @@
         <v>6.8</v>
       </c>
       <c r="AD128">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="AE128">
-        <v>8.1999999999999993</v>
+        <v>6.8</v>
       </c>
       <c r="AF128">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
       <c r="AG128">
         <v>6.3</v>
       </c>
       <c r="AH128">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AI128">
-        <v>6.2</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AJ128">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="AK128">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="AL128">
         <v>7.7</v>
@@ -29229,28 +29229,28 @@
         <v>7.9</v>
       </c>
       <c r="AD129">
-        <v>8.1999999999999993</v>
+        <v>9</v>
       </c>
       <c r="AE129">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="AF129">
-        <v>7.3</v>
+        <v>8.6</v>
       </c>
       <c r="AG129">
         <v>8.5</v>
       </c>
       <c r="AH129">
-        <v>7.9</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AI129">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AJ129">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="AK129">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="AL129">
         <v>7.8</v>
@@ -29411,28 +29411,28 @@
         <v>6.9</v>
       </c>
       <c r="AD130">
+        <v>7.1</v>
+      </c>
+      <c r="AE130">
+        <v>7.3</v>
+      </c>
+      <c r="AF130">
         <v>7</v>
-      </c>
-      <c r="AE130">
-        <v>6.5</v>
-      </c>
-      <c r="AF130">
-        <v>6</v>
       </c>
       <c r="AG130">
         <v>7</v>
       </c>
       <c r="AH130">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="AI130">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AJ130">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="AK130">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="AL130">
         <v>6.8</v>
@@ -29593,28 +29593,28 @@
         <v>7.4</v>
       </c>
       <c r="AD131">
+        <v>7.7</v>
+      </c>
+      <c r="AE131">
         <v>7.2</v>
       </c>
-      <c r="AE131">
-        <v>7</v>
-      </c>
       <c r="AF131">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
       <c r="AG131">
         <v>7.9</v>
       </c>
       <c r="AH131">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AI131">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AJ131">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="AK131">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="AL131">
         <v>7.4</v>
@@ -29775,28 +29775,28 @@
         <v>7.8</v>
       </c>
       <c r="AD132">
-        <v>8.3000000000000007</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="AE132">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AF132">
-        <v>7.5</v>
+        <v>8.9</v>
       </c>
       <c r="AG132">
         <v>8.8000000000000007</v>
       </c>
       <c r="AH132">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="AI132">
+        <v>8</v>
+      </c>
+      <c r="AJ132">
         <v>7.8</v>
       </c>
-      <c r="AI132">
-        <v>8.9</v>
-      </c>
-      <c r="AJ132">
-        <v>8.5</v>
-      </c>
       <c r="AK132">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="AL132">
         <v>7.8</v>
@@ -29957,28 +29957,28 @@
         <v>6.7</v>
       </c>
       <c r="AD133">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE133">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="AF133">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AG133">
         <v>5.9</v>
       </c>
       <c r="AH133">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="AI133">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="AJ133">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="AK133">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="AL133">
         <v>6.3</v>
@@ -30139,28 +30139,28 @@
         <v>7.8</v>
       </c>
       <c r="AD134">
+        <v>6.4</v>
+      </c>
+      <c r="AE134">
+        <v>6.7</v>
+      </c>
+      <c r="AF134">
         <v>6.8</v>
-      </c>
-      <c r="AE134">
-        <v>6.5</v>
-      </c>
-      <c r="AF134">
-        <v>6</v>
       </c>
       <c r="AG134">
         <v>7</v>
       </c>
       <c r="AH134">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AI134">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="AJ134">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="AK134">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AL134">
         <v>7.3</v>
@@ -30321,28 +30321,28 @@
         <v>6.6</v>
       </c>
       <c r="AD135">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="AE135">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AF135">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="AG135">
         <v>7.2</v>
       </c>
       <c r="AH135">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="AI135">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="AJ135">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="AK135">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="AL135">
         <v>6.1</v>
@@ -30503,28 +30503,28 @@
         <v>6.3</v>
       </c>
       <c r="AD136">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AE136">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AF136">
-        <v>5.4</v>
+        <v>6.1</v>
       </c>
       <c r="AG136">
         <v>6.2</v>
       </c>
       <c r="AH136">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
       <c r="AI136">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="AJ136">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AK136">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="AL136">
         <v>6.3</v>
@@ -30685,28 +30685,28 @@
         <v>7.5</v>
       </c>
       <c r="AD137">
-        <v>6.7</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="AE137">
-        <v>6.3</v>
+        <v>7.4</v>
       </c>
       <c r="AF137">
-        <v>5.8</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AG137">
         <v>8.6999999999999993</v>
       </c>
       <c r="AH137">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="AI137">
-        <v>8.6999999999999993</v>
+        <v>6.3</v>
       </c>
       <c r="AJ137">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AK137">
-        <v>7.7</v>
+        <v>5.8</v>
       </c>
       <c r="AL137">
         <v>6.8</v>
@@ -30867,28 +30867,28 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="AD138">
-        <v>6.4</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AE138">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="AF138">
-        <v>5.8</v>
+        <v>7.9</v>
       </c>
       <c r="AG138">
         <v>7.9</v>
       </c>
       <c r="AH138">
-        <v>8.1999999999999993</v>
+        <v>6.4</v>
       </c>
       <c r="AI138">
-        <v>7.9</v>
+        <v>6.3</v>
       </c>
       <c r="AJ138">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="AK138">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="AL138">
         <v>7.2</v>
@@ -31049,28 +31049,28 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="AD139">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="AE139">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AF139">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="AG139">
         <v>8.5</v>
       </c>
       <c r="AH139">
-        <v>8.8000000000000007</v>
+        <v>7</v>
       </c>
       <c r="AI139">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="AJ139">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="AK139">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="AL139">
         <v>8</v>
@@ -31231,28 +31231,28 @@
         <v>7.1</v>
       </c>
       <c r="AD140">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AE140">
-        <v>8.4</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AF140">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="AG140">
         <v>7.2</v>
       </c>
       <c r="AH140">
-        <v>7.1</v>
+        <v>8.6</v>
       </c>
       <c r="AI140">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AJ140">
-        <v>8.3000000000000007</v>
+        <v>7.8</v>
       </c>
       <c r="AK140">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
       <c r="AL140">
         <v>7.7</v>
@@ -31413,28 +31413,28 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="AD141">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="AE141">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AF141">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="AG141">
         <v>7</v>
       </c>
       <c r="AH141">
-        <v>8.1999999999999993</v>
+        <v>6.9</v>
       </c>
       <c r="AI141">
+        <v>7</v>
+      </c>
+      <c r="AJ141">
         <v>6.8</v>
       </c>
-      <c r="AJ141">
-        <v>6.6</v>
-      </c>
       <c r="AK141">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="AL141">
         <v>7.4</v>
@@ -31595,28 +31595,28 @@
         <v>7.8</v>
       </c>
       <c r="AD142">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AE142">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="AF142">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="AG142">
         <v>7.6</v>
       </c>
       <c r="AH142">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AI142">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="AJ142">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="AK142">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="AL142">
         <v>7.4</v>
@@ -31777,28 +31777,28 @@
         <v>7</v>
       </c>
       <c r="AD143">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE143">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="AF143">
-        <v>5.0999999999999996</v>
+        <v>7.5</v>
       </c>
       <c r="AG143">
         <v>7.6</v>
       </c>
       <c r="AH143">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI143">
-        <v>7.5</v>
+        <v>5.6</v>
       </c>
       <c r="AJ143">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="AK143">
-        <v>7.3</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="AL143">
         <v>6.3</v>
@@ -31959,28 +31959,28 @@
         <v>7</v>
       </c>
       <c r="AD144">
-        <v>5.7</v>
+        <v>7.1</v>
       </c>
       <c r="AE144">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
       <c r="AF144">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="AG144">
         <v>7.5</v>
       </c>
       <c r="AH144">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="AI144">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="AJ144">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="AK144">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="AL144">
         <v>6.4</v>
@@ -32141,28 +32141,28 @@
         <v>7.4</v>
       </c>
       <c r="AD145">
+        <v>7.5</v>
+      </c>
+      <c r="AE145">
+        <v>7.3</v>
+      </c>
+      <c r="AF145">
         <v>7.2</v>
-      </c>
-      <c r="AE145">
-        <v>7</v>
-      </c>
-      <c r="AF145">
-        <v>6.5</v>
       </c>
       <c r="AG145">
         <v>7.2</v>
       </c>
       <c r="AH145">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AI145">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AJ145">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="AK145">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="AL145">
         <v>7.2</v>
@@ -32323,28 +32323,28 @@
         <v>8.4</v>
       </c>
       <c r="AD146">
-        <v>7.3</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="AE146">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="AF146">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AG146">
         <v>8.6</v>
       </c>
       <c r="AH146">
-        <v>8.4</v>
+        <v>7.3</v>
       </c>
       <c r="AI146">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
       <c r="AJ146">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="AK146">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AL146">
         <v>7.5</v>
@@ -32505,28 +32505,28 @@
         <v>5.2</v>
       </c>
       <c r="AD147">
-        <v>8.5</v>
+        <v>4.3</v>
       </c>
       <c r="AE147">
-        <v>8.1999999999999993</v>
+        <v>7.7</v>
       </c>
       <c r="AF147">
-        <v>7.7</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AG147">
         <v>4.9000000000000004</v>
       </c>
       <c r="AH147">
-        <v>5.2</v>
+        <v>8.5</v>
       </c>
       <c r="AI147">
-        <v>4.9000000000000004</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AJ147">
+        <v>7.5</v>
+      </c>
+      <c r="AK147">
         <v>7.7</v>
-      </c>
-      <c r="AK147">
-        <v>6.3</v>
       </c>
       <c r="AL147">
         <v>8</v>
@@ -32687,28 +32687,28 @@
         <v>6</v>
       </c>
       <c r="AD148">
-        <v>8.1999999999999993</v>
+        <v>3.3</v>
       </c>
       <c r="AE148">
-        <v>8.1999999999999993</v>
+        <v>6.9</v>
       </c>
       <c r="AF148">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="AG148">
         <v>4.7</v>
       </c>
       <c r="AH148">
-        <v>6</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AI148">
-        <v>4.5</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AJ148">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="AK148">
-        <v>6.6</v>
+        <v>7.7</v>
       </c>
       <c r="AL148">
         <v>7.5</v>
@@ -32869,28 +32869,28 @@
         <v>7.5</v>
       </c>
       <c r="AD149">
-        <v>9.1</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AE149">
-        <v>8.9</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="AF149">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="AG149">
         <v>8</v>
       </c>
       <c r="AH149">
-        <v>7.5</v>
+        <v>9.1</v>
       </c>
       <c r="AI149">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="AJ149">
-        <v>8.8000000000000007</v>
+        <v>8.4</v>
       </c>
       <c r="AK149">
-        <v>7.3</v>
+        <v>8.4</v>
       </c>
       <c r="AL149">
         <v>8.1</v>
@@ -33051,28 +33051,28 @@
         <v>7.8</v>
       </c>
       <c r="AD150">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AE150">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="AF150">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AG150">
         <v>7.2</v>
       </c>
       <c r="AH150">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AI150">
-        <v>7.2</v>
+        <v>8.5</v>
       </c>
       <c r="AJ150">
         <v>8.1</v>
       </c>
       <c r="AK150">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AL150">
         <v>8.4</v>
@@ -33233,28 +33233,28 @@
         <v>7.6</v>
       </c>
       <c r="AD151">
-        <v>8.5</v>
+        <v>6.9</v>
       </c>
       <c r="AE151">
-        <v>8.3000000000000007</v>
+        <v>8.1</v>
       </c>
       <c r="AF151">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
       <c r="AG151">
         <v>7.1</v>
       </c>
       <c r="AH151">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="AI151">
-        <v>7.1</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AJ151">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="AK151">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AL151">
         <v>7.9</v>
@@ -33415,28 +33415,28 @@
         <v>7.3</v>
       </c>
       <c r="AD152">
-        <v>8.8000000000000007</v>
+        <v>7.3</v>
       </c>
       <c r="AE152">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="AF152">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="AG152">
         <v>7.3</v>
       </c>
       <c r="AH152">
-        <v>7.3</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="AI152">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="AJ152">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="AK152">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="AL152">
         <v>7.9</v>
@@ -33597,28 +33597,28 @@
         <v>7.7</v>
       </c>
       <c r="AD153">
+        <v>7.2</v>
+      </c>
+      <c r="AE153">
         <v>7.5</v>
       </c>
-      <c r="AE153">
+      <c r="AF153">
         <v>7.3</v>
-      </c>
-      <c r="AF153">
-        <v>6.8</v>
       </c>
       <c r="AG153">
         <v>7.4</v>
       </c>
       <c r="AH153">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="AI153">
         <v>7.3</v>
       </c>
       <c r="AJ153">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="AK153">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AL153">
         <v>7.7</v>
@@ -33779,28 +33779,28 @@
         <v>7.9</v>
       </c>
       <c r="AD154">
-        <v>8.1</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="AE154">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AF154">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="AG154">
         <v>8.4</v>
       </c>
       <c r="AH154">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="AI154">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="AJ154">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
       <c r="AK154">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="AL154">
         <v>7.8</v>
@@ -33961,13 +33961,13 @@
         <v>7.7</v>
       </c>
       <c r="AD155">
-        <v>7.7</v>
+        <v>9.1</v>
       </c>
       <c r="AE155">
         <v>7.8</v>
       </c>
       <c r="AF155">
-        <v>7.3</v>
+        <v>8.4</v>
       </c>
       <c r="AG155">
         <v>8.3000000000000007</v>
@@ -33976,13 +33976,13 @@
         <v>7.7</v>
       </c>
       <c r="AI155">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AJ155">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AK155">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="AL155">
         <v>7.9</v>
@@ -34143,28 +34143,28 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="AD156">
-        <v>7.8</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AE156">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="AF156">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="AG156">
         <v>7.9</v>
       </c>
       <c r="AH156">
-        <v>8.1999999999999993</v>
+        <v>7.8</v>
       </c>
       <c r="AI156">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="AJ156">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="AK156">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
       <c r="AL156">
         <v>7.9</v>
@@ -34325,28 +34325,28 @@
         <v>8</v>
       </c>
       <c r="AD157">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="AE157">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="AF157">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AG157">
         <v>7.4</v>
       </c>
       <c r="AH157">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="AI157">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="AJ157">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AK157">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AL157">
         <v>7.5</v>
@@ -34507,28 +34507,28 @@
         <v>7</v>
       </c>
       <c r="AD158">
-        <v>7.5</v>
+        <v>5.6</v>
       </c>
       <c r="AE158">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AF158">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="AG158">
         <v>6.6</v>
       </c>
       <c r="AH158">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AI158">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="AJ158">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AK158">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="AL158">
         <v>7.6</v>
@@ -34689,28 +34689,28 @@
         <v>6.8</v>
       </c>
       <c r="AD159">
-        <v>8.6</v>
+        <v>6</v>
       </c>
       <c r="AE159">
-        <v>8.6999999999999993</v>
+        <v>7.7</v>
       </c>
       <c r="AF159">
-        <v>8.1999999999999993</v>
+        <v>6.2</v>
       </c>
       <c r="AG159">
         <v>6.3</v>
       </c>
       <c r="AH159">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AI159">
-        <v>6.2</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AJ159">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="AK159">
-        <v>7.1</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AL159">
         <v>8.1999999999999993</v>
@@ -34871,28 +34871,28 @@
         <v>6.7</v>
       </c>
       <c r="AD160">
-        <v>8.1999999999999993</v>
+        <v>6.3</v>
       </c>
       <c r="AE160">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="AF160">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
       <c r="AG160">
         <v>6.6</v>
       </c>
       <c r="AH160">
-        <v>6.7</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AI160">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AJ160">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="AK160">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AL160">
         <v>7.7</v>
@@ -35053,28 +35053,28 @@
         <v>6.7</v>
       </c>
       <c r="AD161">
-        <v>7.9</v>
+        <v>4.7</v>
       </c>
       <c r="AE161">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF161">
-        <v>7.5</v>
+        <v>5.4</v>
       </c>
       <c r="AG161">
         <v>5.6</v>
       </c>
       <c r="AH161">
-        <v>6.7</v>
+        <v>7.9</v>
       </c>
       <c r="AI161">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="AJ161">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AK161">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AL161">
         <v>7.8</v>
@@ -35235,28 +35235,28 @@
         <v>6.6</v>
       </c>
       <c r="AD162">
-        <v>8.1</v>
+        <v>4.5</v>
       </c>
       <c r="AE162">
-        <v>8.3000000000000007</v>
+        <v>7</v>
       </c>
       <c r="AF162">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="AG162">
         <v>5.6</v>
       </c>
       <c r="AH162">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
       <c r="AI162">
-        <v>5.4</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AJ162">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="AK162">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="AL162">
         <v>8.5</v>
@@ -35417,28 +35417,28 @@
         <v>5.3</v>
       </c>
       <c r="AD163">
-        <v>8.9</v>
+        <v>3.4</v>
       </c>
       <c r="AE163">
-        <v>8.8000000000000007</v>
+        <v>7.4</v>
       </c>
       <c r="AF163">
-        <v>8.3000000000000007</v>
+        <v>4.2</v>
       </c>
       <c r="AG163">
         <v>4.4000000000000004</v>
       </c>
       <c r="AH163">
-        <v>5.3</v>
+        <v>8.9</v>
       </c>
       <c r="AI163">
-        <v>4.2</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="AJ163">
-        <v>7.4</v>
+        <v>8.1</v>
       </c>
       <c r="AK163">
-        <v>6.6</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AL163">
         <v>8.1</v>
@@ -35599,28 +35599,28 @@
         <v>6.8</v>
       </c>
       <c r="AD164">
-        <v>8.1</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AE164">
-        <v>8.3000000000000007</v>
+        <v>7</v>
       </c>
       <c r="AF164">
-        <v>7.8</v>
+        <v>5.6</v>
       </c>
       <c r="AG164">
         <v>5.8</v>
       </c>
       <c r="AH164">
-        <v>6.8</v>
+        <v>8.1</v>
       </c>
       <c r="AI164">
-        <v>5.6</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AJ164">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="AK164">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AL164">
         <v>8.1999999999999993</v>
@@ -35778,28 +35778,28 @@
         <v>8.1</v>
       </c>
       <c r="AD165">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="AE165">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="AF165">
-        <v>7.2</v>
+        <v>7.9</v>
       </c>
       <c r="AG165">
         <v>7.9</v>
       </c>
       <c r="AH165">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="AI165">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="AJ165">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AK165">
-        <v>8.3000000000000007</v>
+        <v>7.2</v>
       </c>
       <c r="AL165">
         <v>8.1999999999999993</v>
@@ -35957,28 +35957,28 @@
         <v>8</v>
       </c>
       <c r="AD166">
-        <v>7.9</v>
+        <v>9.4</v>
       </c>
       <c r="AE166">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="AF166">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="AG166">
         <v>8.4</v>
       </c>
       <c r="AH166">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="AI166">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="AJ166">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="AK166">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="AL166">
         <v>7.6</v>
@@ -36142,22 +36142,22 @@
         <v>7.9</v>
       </c>
       <c r="AF167">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="AG167">
         <v>7.9</v>
       </c>
       <c r="AH167">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AI167">
         <v>7.9</v>
       </c>
       <c r="AJ167">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="AK167">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="AL167">
         <v>7.8</v>
@@ -36315,28 +36315,28 @@
         <v>7.6</v>
       </c>
       <c r="AD168">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="AE168">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AF168">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="AG168">
         <v>7.1</v>
       </c>
       <c r="AH168">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="AI168">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="AJ168">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AK168">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="AL168">
         <v>7.4</v>
@@ -36494,28 +36494,28 @@
         <v>8</v>
       </c>
       <c r="AD169">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="AE169">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="AF169">
-        <v>6.1</v>
+        <v>6.9</v>
       </c>
       <c r="AG169">
         <v>7</v>
       </c>
       <c r="AH169">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="AI169">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="AJ169">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
       <c r="AK169">
-        <v>7.3</v>
+        <v>6.1</v>
       </c>
       <c r="AL169">
         <v>7.1</v>
@@ -36676,28 +36676,28 @@
         <v>6.4</v>
       </c>
       <c r="AD170">
-        <v>7.4</v>
+        <v>3.9</v>
       </c>
       <c r="AE170">
-        <v>7.7</v>
+        <v>6.1</v>
       </c>
       <c r="AF170">
-        <v>7.2</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AG170">
         <v>5.2</v>
       </c>
       <c r="AH170">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AI170">
-        <v>4.9000000000000004</v>
+        <v>7.7</v>
       </c>
       <c r="AJ170">
-        <v>6.1</v>
+        <v>7.1</v>
       </c>
       <c r="AK170">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AL170">
         <v>8.1</v>
@@ -36858,28 +36858,28 @@
         <v>4.5</v>
       </c>
       <c r="AD171">
-        <v>8.6999999999999993</v>
+        <v>2.9</v>
       </c>
       <c r="AE171">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="AF171">
-        <v>8.5</v>
+        <v>3.6</v>
       </c>
       <c r="AG171">
         <v>3.8</v>
       </c>
       <c r="AH171">
-        <v>4.5</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AI171">
-        <v>3.6</v>
+        <v>9</v>
       </c>
       <c r="AJ171">
-        <v>6.8</v>
+        <v>7.9</v>
       </c>
       <c r="AK171">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="AL171">
         <v>8.1999999999999993</v>
@@ -37040,28 +37040,28 @@
         <v>5.2</v>
       </c>
       <c r="AD172">
-        <v>8.6999999999999993</v>
+        <v>3.9</v>
       </c>
       <c r="AE172">
-        <v>8.8000000000000007</v>
+        <v>7.3</v>
       </c>
       <c r="AF172">
-        <v>8.3000000000000007</v>
+        <v>4.3</v>
       </c>
       <c r="AG172">
         <v>4.3</v>
       </c>
       <c r="AH172">
-        <v>5.2</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AI172">
-        <v>4.3</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="AJ172">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="AK172">
-        <v>6.6</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AL172">
         <v>8.9</v>
@@ -37222,28 +37222,28 @@
         <v>9</v>
       </c>
       <c r="AD173">
-        <v>7.3</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="AE173">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="AF173">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="AG173">
         <v>9</v>
       </c>
       <c r="AH173">
-        <v>9</v>
+        <v>7.3</v>
       </c>
       <c r="AI173">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AJ173">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="AK173">
-        <v>8.6999999999999993</v>
+        <v>6.5</v>
       </c>
       <c r="AL173">
         <v>8</v>
@@ -37404,28 +37404,28 @@
         <v>8.5</v>
       </c>
       <c r="AD174">
-        <v>8.1</v>
+        <v>9.6</v>
       </c>
       <c r="AE174">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="AF174">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
       <c r="AG174">
         <v>8.8000000000000007</v>
       </c>
       <c r="AH174">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="AI174">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="AJ174">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="AK174">
-        <v>8.1999999999999993</v>
+        <v>7.4</v>
       </c>
       <c r="AL174">
         <v>8.1999999999999993</v>
@@ -37586,28 +37586,28 @@
         <v>8.1</v>
       </c>
       <c r="AD175">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="AE175">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="AF175">
-        <v>6.9</v>
+        <v>7.8</v>
       </c>
       <c r="AG175">
         <v>7.8</v>
       </c>
       <c r="AH175">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="AI175">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AJ175">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="AK175">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="AL175">
         <v>7.9</v>
@@ -37768,28 +37768,28 @@
         <v>7.2</v>
       </c>
       <c r="AD176">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="AE176">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AF176">
-        <v>6.1</v>
+        <v>7.2</v>
       </c>
       <c r="AG176">
         <v>7.2</v>
       </c>
       <c r="AH176">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
       <c r="AI176">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AJ176">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AK176">
-        <v>7.4</v>
+        <v>6.1</v>
       </c>
       <c r="AL176">
         <v>7</v>
@@ -37950,28 +37950,28 @@
         <v>7</v>
       </c>
       <c r="AD177">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="AE177">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AF177">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="AG177">
         <v>6.5</v>
       </c>
       <c r="AH177">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AI177">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AJ177">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="AK177">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="AL177">
         <v>7.4</v>
@@ -38132,28 +38132,28 @@
         <v>7.4</v>
       </c>
       <c r="AD178">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AE178">
         <v>7.4</v>
       </c>
       <c r="AF178">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="AG178">
         <v>7.2</v>
       </c>
       <c r="AH178">
+        <v>7.6</v>
+      </c>
+      <c r="AI178">
         <v>7.4</v>
       </c>
-      <c r="AI178">
-        <v>7.1</v>
-      </c>
       <c r="AJ178">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AK178">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="AL178">
         <v>7.4</v>
@@ -38314,28 +38314,28 @@
         <v>5.5</v>
       </c>
       <c r="AD179">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="AE179">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="AF179">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="AG179">
         <v>6.3</v>
       </c>
       <c r="AH179">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AI179">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="AJ179">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="AK179">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="AL179">
         <v>6.2</v>
@@ -38496,28 +38496,28 @@
         <v>5.7</v>
       </c>
       <c r="AD180">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AE180">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="AF180">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="AG180">
         <v>6.4</v>
       </c>
       <c r="AH180">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="AI180">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="AJ180">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="AK180">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
       <c r="AL180">
         <v>7</v>
@@ -38678,28 +38678,28 @@
         <v>6.4</v>
       </c>
       <c r="AD181">
-        <v>8.6999999999999993</v>
+        <v>3.9</v>
       </c>
       <c r="AE181">
-        <v>8.8000000000000007</v>
+        <v>7.2</v>
       </c>
       <c r="AF181">
-        <v>8.3000000000000007</v>
+        <v>4.7</v>
       </c>
       <c r="AG181">
         <v>4.9000000000000004</v>
       </c>
       <c r="AH181">
-        <v>6.4</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AI181">
-        <v>4.7</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="AJ181">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AK181">
-        <v>7.4</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AL181">
         <v>8.8000000000000007</v>
@@ -38860,28 +38860,28 @@
         <v>8</v>
       </c>
       <c r="AD182">
-        <v>9.5</v>
+        <v>4.8</v>
       </c>
       <c r="AE182">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AF182">
-        <v>8.5</v>
+        <v>6.2</v>
       </c>
       <c r="AG182">
         <v>6.6</v>
       </c>
       <c r="AH182">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="AI182">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AJ182">
+        <v>9</v>
+      </c>
+      <c r="AK182">
         <v>8.5</v>
-      </c>
-      <c r="AK182">
-        <v>9.5</v>
       </c>
       <c r="AL182">
         <v>9.5</v>
@@ -39039,28 +39039,28 @@
         <v>6.9</v>
       </c>
       <c r="AD183">
-        <v>8.9</v>
+        <v>4.5</v>
       </c>
       <c r="AE183">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
       <c r="AF183">
-        <v>8.6</v>
+        <v>5.4</v>
       </c>
       <c r="AG183">
         <v>5.6</v>
       </c>
       <c r="AH183">
-        <v>6.9</v>
+        <v>8.9</v>
       </c>
       <c r="AI183">
-        <v>5.4</v>
+        <v>9.1</v>
       </c>
       <c r="AJ183">
-        <v>7.5</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AK183">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AL183">
         <v>9</v>
@@ -39221,28 +39221,28 @@
         <v>5.9</v>
       </c>
       <c r="AD184">
-        <v>7.5</v>
+        <v>1.9</v>
       </c>
       <c r="AE184">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="AF184">
-        <v>7.5</v>
+        <v>3.3</v>
       </c>
       <c r="AG184">
         <v>3.8</v>
       </c>
       <c r="AH184">
-        <v>5.9</v>
+        <v>7.5</v>
       </c>
       <c r="AI184">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="AJ184">
-        <v>5.4</v>
+        <v>7.3</v>
       </c>
       <c r="AK184">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AL184">
         <v>8.5</v>
@@ -39403,28 +39403,28 @@
         <v>6.2</v>
       </c>
       <c r="AD185">
-        <v>8.5</v>
+        <v>5.3</v>
       </c>
       <c r="AE185">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="AF185">
-        <v>7.9</v>
+        <v>6.3</v>
       </c>
       <c r="AG185">
         <v>6.4</v>
       </c>
       <c r="AH185">
-        <v>6.2</v>
+        <v>8.5</v>
       </c>
       <c r="AI185">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
       <c r="AJ185">
         <v>7.9</v>
       </c>
       <c r="AK185">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="AL185">
         <v>7.7</v>
@@ -39585,28 +39585,28 @@
         <v>6.2</v>
       </c>
       <c r="AD186">
-        <v>9</v>
+        <v>4.3</v>
       </c>
       <c r="AE186">
-        <v>9</v>
+        <v>7.7</v>
       </c>
       <c r="AF186">
-        <v>8.5</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="AG186">
         <v>5.2</v>
       </c>
       <c r="AH186">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AI186">
-        <v>5.0999999999999996</v>
+        <v>9</v>
       </c>
       <c r="AJ186">
-        <v>7.7</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AK186">
-        <v>6.6</v>
+        <v>8.5</v>
       </c>
       <c r="AL186">
         <v>8.1999999999999993</v>
@@ -39767,28 +39767,28 @@
         <v>7</v>
       </c>
       <c r="AD187">
-        <v>8.3000000000000007</v>
+        <v>4.3</v>
       </c>
       <c r="AE187">
-        <v>8.6</v>
+        <v>6.9</v>
       </c>
       <c r="AF187">
-        <v>8.1</v>
+        <v>5.3</v>
       </c>
       <c r="AG187">
         <v>5.6</v>
       </c>
       <c r="AH187">
-        <v>7</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AI187">
-        <v>5.3</v>
+        <v>8.6</v>
       </c>
       <c r="AJ187">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="AK187">
-        <v>8.1999999999999993</v>
+        <v>8.1</v>
       </c>
       <c r="AL187">
         <v>8.9</v>
@@ -39949,28 +39949,28 @@
         <v>6.7</v>
       </c>
       <c r="AD188">
-        <v>9.1999999999999993</v>
+        <v>4.8</v>
       </c>
       <c r="AE188">
-        <v>9</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AF188">
-        <v>8.5</v>
+        <v>5.8</v>
       </c>
       <c r="AG188">
         <v>5.9</v>
       </c>
       <c r="AH188">
-        <v>6.7</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="AI188">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AJ188">
-        <v>8.1999999999999993</v>
+        <v>8.4</v>
       </c>
       <c r="AK188">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="AL188">
         <v>8.4</v>
@@ -40131,28 +40131,28 @@
         <v>7.2</v>
       </c>
       <c r="AD189">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="AE189">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="AF189">
-        <v>6.1</v>
+        <v>7.7</v>
       </c>
       <c r="AG189">
         <v>7.7</v>
       </c>
       <c r="AH189">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="AI189">
-        <v>7.7</v>
+        <v>6.6</v>
       </c>
       <c r="AJ189">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
       <c r="AK189">
-        <v>7.3</v>
+        <v>6.1</v>
       </c>
       <c r="AL189">
         <v>7</v>
@@ -40313,28 +40313,28 @@
         <v>7.7</v>
       </c>
       <c r="AD190">
-        <v>8.6</v>
+        <v>6.9</v>
       </c>
       <c r="AE190">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AF190">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
       <c r="AG190">
         <v>7.2</v>
       </c>
       <c r="AH190">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
       <c r="AI190">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AJ190">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="AK190">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="AL190">
         <v>8.1999999999999993</v>
@@ -40495,28 +40495,28 @@
         <v>7.4</v>
       </c>
       <c r="AD191">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
       <c r="AE191">
-        <v>8.6999999999999993</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AF191">
-        <v>8.1999999999999993</v>
+        <v>7.5</v>
       </c>
       <c r="AG191">
         <v>7.5</v>
       </c>
       <c r="AH191">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AI191">
-        <v>7.5</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AJ191">
+        <v>8.1</v>
+      </c>
+      <c r="AK191">
         <v>8.1999999999999993</v>
-      </c>
-      <c r="AK191">
-        <v>7.4</v>
       </c>
       <c r="AL191">
         <v>8.1</v>
@@ -40677,28 +40677,28 @@
         <v>4.7</v>
       </c>
       <c r="AD192">
-        <v>9.1999999999999993</v>
+        <v>2.9</v>
       </c>
       <c r="AE192">
-        <v>9.5</v>
+        <v>7.2</v>
       </c>
       <c r="AF192">
-        <v>9</v>
+        <v>3.6</v>
       </c>
       <c r="AG192">
         <v>3.7</v>
       </c>
       <c r="AH192">
-        <v>4.7</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="AI192">
-        <v>3.6</v>
+        <v>9.5</v>
       </c>
       <c r="AJ192">
-        <v>7.2</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AK192">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AL192">
         <v>8.4</v>
@@ -40859,28 +40859,28 @@
         <v>6.5</v>
       </c>
       <c r="AD193">
-        <v>9.5</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="AE193">
-        <v>9.6</v>
+        <v>7.7</v>
       </c>
       <c r="AF193">
-        <v>9.1</v>
+        <v>4.8</v>
       </c>
       <c r="AG193">
         <v>5.0999999999999996</v>
       </c>
       <c r="AH193">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="AI193">
-        <v>4.8</v>
+        <v>9.6</v>
       </c>
       <c r="AJ193">
-        <v>7.7</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="AK193">
-        <v>7.9</v>
+        <v>9.1</v>
       </c>
       <c r="AL193">
         <v>9.4</v>
@@ -41035,28 +41035,28 @@
         <v>7.5</v>
       </c>
       <c r="AD194">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AE194">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="AF194">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="AG194">
         <v>8.4</v>
       </c>
       <c r="AH194">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="AI194">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="AJ194">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="AK194">
-        <v>7.7</v>
+        <v>6.5</v>
       </c>
       <c r="AL194">
         <v>7.4</v>
@@ -41217,28 +41217,28 @@
         <v>6</v>
       </c>
       <c r="AD195">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AE195">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AF195">
-        <v>4.5</v>
+        <v>6.3</v>
       </c>
       <c r="AG195">
         <v>6.3</v>
       </c>
       <c r="AH195">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AI195">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="AJ195">
-        <v>5.9</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="AK195">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="AL195">
         <v>5.9</v>
@@ -41399,13 +41399,13 @@
         <v>7.8</v>
       </c>
       <c r="AD196">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AE196">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="AF196">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="AG196">
         <v>7.4</v>
@@ -41414,13 +41414,13 @@
         <v>7.8</v>
       </c>
       <c r="AI196">
+        <v>7.8</v>
+      </c>
+      <c r="AJ196">
         <v>7.4</v>
       </c>
-      <c r="AJ196">
-        <v>7.7</v>
-      </c>
       <c r="AK196">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="AL196">
         <v>7.9</v>
@@ -41581,28 +41581,28 @@
         <v>6.9</v>
       </c>
       <c r="AD197">
-        <v>8.6999999999999993</v>
+        <v>7.3</v>
       </c>
       <c r="AE197">
-        <v>8.5</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AF197">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="AG197">
         <v>7.1</v>
       </c>
       <c r="AH197">
-        <v>6.9</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AI197">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="AJ197">
-        <v>8.3000000000000007</v>
+        <v>8</v>
       </c>
       <c r="AK197">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AL197">
         <v>8.1999999999999993</v>
@@ -41763,28 +41763,28 @@
         <v>6.1</v>
       </c>
       <c r="AD198">
-        <v>9.5</v>
+        <v>6.6</v>
       </c>
       <c r="AE198">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AF198">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="AG198">
         <v>6.1</v>
       </c>
       <c r="AH198">
-        <v>6.1</v>
+        <v>9.5</v>
       </c>
       <c r="AI198">
-        <v>6.2</v>
+        <v>9.5</v>
       </c>
       <c r="AJ198">
         <v>8.5</v>
       </c>
       <c r="AK198">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="AL198">
         <v>7.9</v>
@@ -41945,28 +41945,28 @@
         <v>7.2</v>
       </c>
       <c r="AD199">
-        <v>8.5</v>
+        <v>5.4</v>
       </c>
       <c r="AE199">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="AF199">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="AG199">
         <v>6.6</v>
       </c>
       <c r="AH199">
-        <v>7.2</v>
+        <v>8.5</v>
       </c>
       <c r="AI199">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="AJ199">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AK199">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="AL199">
         <v>8.3000000000000007</v>
@@ -42127,28 +42127,28 @@
         <v>7.1</v>
       </c>
       <c r="AD200">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="AE200">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
       <c r="AF200">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="AG200">
         <v>7.2</v>
       </c>
       <c r="AH200">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="AI200">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AJ200">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="AK200">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="AL200">
         <v>7.7</v>
@@ -42309,28 +42309,28 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="AD201">
-        <v>8.3000000000000007</v>
+        <v>3.2</v>
       </c>
       <c r="AE201">
-        <v>8.4</v>
+        <v>6.9</v>
       </c>
       <c r="AF201">
-        <v>7.9</v>
+        <v>4.3</v>
       </c>
       <c r="AG201">
         <v>4.5</v>
       </c>
       <c r="AH201">
-        <v>5.0999999999999996</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AI201">
-        <v>4.3</v>
+        <v>8.4</v>
       </c>
       <c r="AJ201">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="AK201">
-        <v>6.2</v>
+        <v>7.9</v>
       </c>
       <c r="AL201">
         <v>7.6</v>
@@ -42491,28 +42491,28 @@
         <v>7</v>
       </c>
       <c r="AD202">
-        <v>7.9</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AE202">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF202">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="AG202">
         <v>5.6</v>
       </c>
       <c r="AH202">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="AI202">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="AJ202">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AK202">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="AL202">
         <v>8.1999999999999993</v>
@@ -42673,28 +42673,28 @@
         <v>7.2</v>
       </c>
       <c r="AD203">
-        <v>8.4</v>
+        <v>5.2</v>
       </c>
       <c r="AE203">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AF203">
-        <v>7.9</v>
+        <v>6.1</v>
       </c>
       <c r="AG203">
         <v>6.3</v>
       </c>
       <c r="AH203">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AI203">
-        <v>6.1</v>
+        <v>8.4</v>
       </c>
       <c r="AJ203">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="AK203">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="AL203">
         <v>8.3000000000000007</v>
@@ -42855,28 +42855,28 @@
         <v>7.5</v>
       </c>
       <c r="AD204">
-        <v>8.6999999999999993</v>
+        <v>6.1</v>
       </c>
       <c r="AE204">
-        <v>9</v>
+        <v>7.9</v>
       </c>
       <c r="AF204">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="AG204">
         <v>7.2</v>
       </c>
       <c r="AH204">
-        <v>7.5</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AI204">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="AJ204">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="AK204">
-        <v>8.3000000000000007</v>
+        <v>8.5</v>
       </c>
       <c r="AL204">
         <v>8.9</v>
@@ -43031,28 +43031,28 @@
         <v>7.6</v>
       </c>
       <c r="AD205">
-        <v>8.6</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AE205">
-        <v>8.3000000000000007</v>
+        <v>8.5</v>
       </c>
       <c r="AF205">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AG205">
         <v>7.9</v>
       </c>
       <c r="AH205">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AI205">
-        <v>8</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AJ205">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="AK205">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AL205">
         <v>7.9</v>
@@ -43213,28 +43213,28 @@
         <v>8.5</v>
       </c>
       <c r="AD206">
-        <v>6.9</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="AE206">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="AF206">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="AG206">
         <v>9</v>
       </c>
       <c r="AH206">
-        <v>8.5</v>
+        <v>6.9</v>
       </c>
       <c r="AI206">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AJ206">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="AK206">
-        <v>8.8000000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="AL206">
         <v>8</v>
@@ -43401,28 +43401,28 @@
         <v>6.9</v>
       </c>
       <c r="AD207">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="AE207">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="AF207">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AG207">
         <v>6.2</v>
       </c>
       <c r="AH207">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="AI207">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="AJ207">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="AK207">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AL207">
         <v>7.2</v>
@@ -43577,28 +43577,28 @@
         <v>7.8</v>
       </c>
       <c r="AD208">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AE208">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="AF208">
-        <v>5.3</v>
+        <v>7.1</v>
       </c>
       <c r="AG208">
         <v>7.2</v>
       </c>
       <c r="AH208">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="AI208">
-        <v>7.1</v>
+        <v>5.8</v>
       </c>
       <c r="AJ208">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AK208">
-        <v>8.1</v>
+        <v>5.3</v>
       </c>
       <c r="AL208">
         <v>7.1</v>
@@ -43682,7 +43682,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22E987F2-6BC8-4D9A-B479-5495D121D72B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77D991EE-B585-466B-A94F-C10210E23607}">
   <dimension ref="A1:K896"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
